--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Generic/AdminApp_Generic_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Generic/AdminApp_Generic_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="288">
   <si>
     <t>S.No.</t>
   </si>
@@ -81,10 +81,10 @@
   </si>
   <si>
     <t xml:space="preserve">Exactly TWO options are offered, in this order: "English", then "Español".
-The active language ("English") is visually marked as the selected option, and the control's accessible name reads "Site language, English".</t>
-  </si>
-  <si>
-    <t>Grounded live 2026-08-27 from the pre-rendered DOM. Control qid "sp-ldd-cntr"; options "sp-ldd-btn-en" and "sp-ldd-btn-es". Selection is marked by the CSS class "selected-item" on the active option — that class, not styling, is the reliable check. The control appears in the HEADER when logged out and the FOOTER when logged in. DISTINCT FROM TST_LAND_TC_4, which covers the same control on the LANDING page — this case is the admin-app instance.</t>
+The active language ("English") carries the CSS class "active" and its accessible name ends ", selected"; the trigger's accessible name reads "Site language, English".</t>
+  </si>
+  <si>
+    <t>**[CORRECTED 2026-09-14 — live pass]** Logged-in qids were WRONG: the trigger is "cFooter-7" and the options are "cFooter-8-0" (English) and "cFooter-8-1" (Español) — "sp-ldd-*" does not exist when logged in (it is presumably the logged-out header control). The active option is marked by class "active", NOT "selected-item". — Superseded note follows: Grounded live 2026-08-27 from the pre-rendered DOM. Control qid "sp-ldd-cntr"; options "sp-ldd-btn-en" and "sp-ldd-btn-es". Selection is marked by the CSS class "selected-item" on the active option — that class, not styling, is the reliable check. The control appears in the HEADER when logged out and the FOOTER when logged in. DISTINCT FROM TST_LAND_TC_4, which covers the same control on the LANDING page — this case is the admin-app instance.</t>
   </si>
   <si>
     <t/>
@@ -106,15 +106,15 @@
 5. Switch back to "English".</t>
   </si>
   <si>
-    <t>Expected Spanish strings: to be added to appLangES.json once captured (see Remarks).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ASSUMED] After step 2 the admin interface re-renders in Spanish: the "My school accounts" heading, the footer links and the role toggle all show Spanish copy, and the language control now reads "Español" with "Español" marked selected.
-[ASSUMED] After step 4 the Spanish selection PERSISTS across the reload.
-After step 5 the interface returns to English.</t>
-  </si>
-  <si>
-    <t>⚠️ NOT GROUNDED — no admin-app Spanish copy has been verified. GENUINE GAP: appLangES.json exists but contains only "landing" and "login" sections — it has NO admin-app or footer entries, so the strings this case needs do not exist yet anywhere. When captured they should be added to appLangES.json under a new admin section, matching the existing appLangEN.json pattern. Whether the choice persists per-account server-side (as the class Filter and Search do, admin-shared.md §A4) or only for the session is specifically unknown. CHANGES ACCOUNT STATE: switches the language and must switch it back (step 5).</t>
+    <t>Verified Spanish copy (2026-09-14): School settings "Pautas del centro educativo"; footer "Términos de uso" · "Aviso de privacidad" · "Accesibilidad" · "Ayuda"; "Cambridge One para centros educativos"; Help "Ayuda"; trigger "Idioma del sitio, Español"; toggle "Interruptor Administrador/Profesor: Administrador actualmente activo, activar para ver el panel del Profesor".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After step 2 the interface re-renders IN PLACE (no reload) in Spanish: html lang becomes "es", Español carries class "active", and the strings listed in Test Data are shown.
+After step 4 the Spanish selection PERSISTS across the reload (stored in the browser's localStorage "comprodls.nemo.selected-locale").
+After step 5 the page RELOADS and returns to English (html lang "en").</t>
+  </si>
+  <si>
+    <t>**[CORRECTED 2026-09-14 — live pass]** GROUNDED LIVE 2026-09-14 on KNF-XRD-QVE (approved by the user). Persistence is PER-BROWSER, not per-account — a fresh browser context starts in English, so other suites are not affected. es→en reloads the page while en→es does not — the restore step must wait for a navigation. I18N DEFECTS found: footer "Our approach" is not translated; the bell's aria-label stays "Notifications (N unread notifications)"; tab "Clases (10)" has a space before the count while the other tabs do not. "Pautas del centro educativo" (≈ guidelines) is a questionable translation — confirm with product. — Superseded note follows: ⚠️ NOT GROUNDED — no admin-app Spanish copy has been verified. GENUINE GAP: appLangES.json exists but contains only "landing" and "login" sections — it has NO admin-app or footer entries, so the strings this case needs do not exist yet anywhere. When captured they should be added to appLangES.json under a new admin section, matching the existing appLangEN.json pattern. Whether the choice persists per-account server-side (as the class Filter and Search do, admin-shared.md §A4) or only for the session is specifically unknown. CHANGES ACCOUNT STATE: switches the language and must switch it back (step 5).</t>
   </si>
   <si>
     <t>TST_MYPR_TC_1</t>
@@ -159,7 +159,7 @@
 Observed 2026-08-27 for &lt;ADMIN_USER&gt;: First name "Test", Last name "T1", Email "testt1@mailsac.com", Location "India".</t>
   </si>
   <si>
-    <t>GROUNDED LIVE 2026-08-27. Field qids "c-mp-inpt-1".."c-mp-inpt-4"; Update "c-mp-btn-3"; Cancel "c-mp-btn-4". Underlying Gigya names: profile.firstName / profile.lastName / profile.email / profile.country. ⚠️ The "Location" field has THREE identities — label "Location", name "profile.country", HTML id "gigya-textbox-zip" (zip, i.e. postcode). It behaves as a country ("India"). Select it by qid, and do not infer its meaning from the id. VALUES ARE ACCOUNT-SPECIFIC — use &lt;ADMIN_USER&gt; placeholders, never the literals above (admin-shared.md §A5).</t>
+    <t>**[CORRECTED 2026-09-14 — live pass]** Update is input[type=submit][value="Update"] (qid "c-mp-btn-3") — assert its value, its text is empty. Cancel on THIS tab is "c-mp-btn-2" — "c-mp-btn-4" is the Password tab's Cancel. Labels carry " *" (visually required) although no field has a required attribute. — Superseded note follows: GROUNDED LIVE 2026-08-27. Field qids "c-mp-inpt-1".."c-mp-inpt-4"; Update "c-mp-btn-3"; Cancel "c-mp-btn-4". Underlying Gigya names: profile.firstName / profile.lastName / profile.email / profile.country. ⚠️ The "Location" field has THREE identities — label "Location", name "profile.country", HTML id "gigya-textbox-zip" (zip, i.e. postcode). It behaves as a country ("India"). Select it by qid, and do not infer its meaning from the id. VALUES ARE ACCOUNT-SPECIFIC — use &lt;ADMIN_USER&gt; placeholders, never the literals above (admin-shared.md §A5).</t>
   </si>
   <si>
     <t>TST_MYPR_TC_3</t>
@@ -181,7 +181,7 @@
 All three inputs mask their content (type=password).</t>
   </si>
   <si>
-    <t>GROUNDED LIVE 2026-08-27. Field qids "c-mp-inpt-5".."c-mp-inpt-7"; Update "c-mp-btn-5". Gigya names: password / newPassword / passwordRetype. ⚠️ The URL does NOT change between tabs — both are /dashboard/my-profile. The Password tab therefore CANNOT be deep-linked, and the active tab cannot be asserted from the URL. Combined with the missing aria-selected (TST_MYPR_TC_8) there is currently NO reliable attribute identifying the active tab — automation must assert on the visible fields instead.</t>
+    <t>**[CORRECTED 2026-09-14 — live pass]** The active tab IS identifiable: the parent li gets class "selected" (li.password-tab … selected) — this corrects "there is currently NO reliable attribute identifying the active tab". Cancel on this tab is "c-mp-btn-4". The tabs swap DOM (Personal-info inputs are removed) and the swap takes more than 1 s. — Superseded note follows: GROUNDED LIVE 2026-08-27. Field qids "c-mp-inpt-5".."c-mp-inpt-7"; Update "c-mp-btn-5". Gigya names: password / newPassword / passwordRetype. ⚠️ The URL does NOT change between tabs — both are /dashboard/my-profile. The Password tab therefore CANNOT be deep-linked, and the active tab cannot be asserted from the URL. Combined with the missing aria-selected (TST_MYPR_TC_8) there is currently NO reliable attribute identifying the active tab — automation must assert on the visible fields instead.</t>
   </si>
   <si>
     <t>TST_MYPR_TC_4</t>
@@ -234,7 +234,7 @@
 [ASSUMED] After step 4 the server rejects the value with a validation message, or accepts and truncates it. Capture which, and the exact message.</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED PARTIALLY 2026-08-27: the ABSENCE of a limit is verified — ALL SEVEN fields across both tabs have maxlength=null and none is marked required. What the SERVER does is [ASSUMED]. This is a deliberate departure from the rest of the admin app, where limits are declared and enforced client-side (class name 50, grading scale title 20 — admin-shared.md §A3). Because nothing is declared here, boundary cases CANNOT be derived from the markup and must be found by submitting. ⚠️ DO NOT RUN ON &lt;ADMIN_USER&gt; — that account is the login for the whole admin suite. Blocked until a disposable account exists.</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED PARTIALLY 2026-08-27: the ABSENCE of a limit is verified — ALL SEVEN fields across both tabs have maxlength=null and none is marked required. What the SERVER does is [ASSUMED]. This is a deliberate departure from the rest of the admin app, where limits are declared and enforced client-side (class name 50, grading scale title 20 — admin-shared.md §A3). Because nothing is declared here, boundary cases CANNOT be derived from the markup and must be found by submitting. ⚠️ DO NOT RUN ON &lt;ADMIN_USER&gt; — that account is the login for the whole admin suite. Blocked until a disposable account exists.</t>
   </si>
   <si>
     <t>TST_MYPR_TC_6</t>
@@ -261,7 +261,7 @@
     <t>[ASSUMED] The password is NOT changed and a mismatch validation message is shown against the confirmation field.</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. ⚠️ ERROR COPY NOT CAPTURED — nothing was submitted, by agreement, because &lt;ADMIN_USER&gt; is the admin suite's login account. The message text must be captured on a disposable account. For reference the equivalent page in the other app exposes a dedicated error element ("confirmPasswordError_text" in the SETT selector set), so a field-level message is expected here too — but that is the OTHER app and must not be assumed identical. DESTRUCTIVE IF IT SUCCEEDS: a mistyped variant of this case would change a real password.</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. ⚠️ ERROR COPY NOT CAPTURED — nothing was submitted, by agreement, because &lt;ADMIN_USER&gt; is the admin suite's login account. The message text must be captured on a disposable account. For reference the equivalent page in the other app exposes a dedicated error element ("confirmPasswordError_text" in the SETT selector set), so a field-level message is expected here too — but that is the OTHER app and must not be assumed identical. DESTRUCTIVE IF IT SUCCEEDS: a mistyped variant of this case would change a real password.</t>
   </si>
   <si>
     <t>TST_MYPR_TC_7</t>
@@ -281,7 +281,7 @@
     <t>[ASSUMED] The password is NOT changed and an error identifies the old password as incorrect.</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. ⚠️ ERROR COPY NOT CAPTURED — see TST_MYPR_TC_6. The SETT selector set has a matching "currentPasswordError_text" element in the other app. Worth checking whether repeated failures lock the account, which would affect suite design.</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. ⚠️ ERROR COPY NOT CAPTURED — see TST_MYPR_TC_6. The SETT selector set has a matching "currentPasswordError_text" element in the other app. Worth checking whether repeated failures lock the account, which would affect suite design.</t>
   </si>
   <si>
     <t>TST_MYPR_TC_8</t>
@@ -299,7 +299,7 @@
 ACTUAL (2026-08-27): this FAILS. Both are plain &lt;a&gt; elements with NO role="tab" and NO aria-selected. Nothing in the markup or the URL identifies the active tab.</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. Raised as a case because it is both an accessibility gap and an automation blocker: with no aria-selected AND no URL change between tabs (TST_MYPR_TC_3), there is no attribute to assert the active tab on — automation must fall back to checking which fields are visible. Confirm with the product team whether this should be raised as a defect. Tab qids "c-mp-tab-1" (Personal info) and "c-mp-tab-2" (Password).</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. Raised as a case because it is both an accessibility gap and an automation blocker: with no aria-selected AND no URL change between tabs (TST_MYPR_TC_3), there is no attribute to assert the active tab on — automation must fall back to checking which fields are visible. Confirm with the product team whether this should be raised as a defect. Tab qids "c-mp-tab-1" (Personal info) and "c-mp-tab-2" (Password).</t>
   </si>
   <si>
     <t>TST_INVI_TC_7</t>
@@ -344,7 +344,7 @@
 Observed 2026-08-27: heading "Notifications (92)" matching the badge; both time groups present.</t>
   </si>
   <si>
-    <t>GROUNDED LIVE 2026-08-27 — the panel was opened manually and read in full, resolving the earlier [ASSUMED] version of this case. GENUINE GAP: TST_INVI_TC_1..6 cover the INVITATION-ACCEPT flow reached through this bell (invitationNotify → selectCheckbox → acceptBtn → goToDashboard); they do NOT cover this panel. Selectors: panel ".notification-dropdown"; heading ".notification-heading" h2 with span.readCount; time groups "p.time-related-title"; rows "button.tippy-dropdown-item"; footer link qid "ntf-4". ⚠️ The close "×" carries qid "ntf-2" on TWO visible elements (".close" and ".close-dummy") — address it by class, not qid. Same trap shape as cFooter-9. NOT pre-rendered — built lazily by tippy.js, so it must actually be opened (admin-shared.md §A6 does not apply here). The EMPTY state was not seen — this account has 92 notifications. [ASSUMED] and still open.</t>
+    <t>**[CORRECTED 2026-09-14 — live pass]** ".notification-dropdown" is the 56 px wrapper AROUND THE BELL, not the panel — do not use it as the panel selector. Count was 93 on 2026-09-14 (never assert an absolute count). Opening the panel does NOT change the unread count (93 before, 93 after). — Superseded note follows: GROUNDED LIVE 2026-08-27 — the panel was opened manually and read in full, resolving the earlier [ASSUMED] version of this case. GENUINE GAP: TST_INVI_TC_1..6 cover the INVITATION-ACCEPT flow reached through this bell (invitationNotify → selectCheckbox → acceptBtn → goToDashboard); they do NOT cover this panel. Selectors: panel ".notification-dropdown"; heading ".notification-heading" h2 with span.readCount; time groups "p.time-related-title"; rows "button.tippy-dropdown-item"; footer link qid "ntf-4". ⚠️ The close "×" carries qid "ntf-2" on TWO visible elements (".close" and ".close-dummy") — address it by class, not qid. Same trap shape as cFooter-9. NOT pre-rendered — built lazily by tippy.js, so it must actually be opened (admin-shared.md §A6 does not apply here). The EMPTY state was not seen — this account has 92 notifications. [ASSUMED] and still open.</t>
   </si>
   <si>
     <t>TST_INVI_TC_9</t>
@@ -399,19 +399,18 @@
     <t>Low</t>
   </si>
   <si>
-    <t>Logged in as school-admin &lt;ADMIN_USER&gt; on Thor; "My school accounts" (/admin/admin/dashboard) displayed. The account has both "Class summary" and "Aggregated data" report-ready notifications.</t>
+    <t>Logged in as school-admin &lt;ADMIN_USER&gt; on Thor; "My school accounts" (/admin/admin/dashboard) displayed. The account has report-ready notifications of more than one report type.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Click the notifications bell.
-2. Read the body line of a "Your Class summary report is ready" row.
-3. Read the body line of a "Your Aggregated data report is ready" row.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Both notifications refer to the same destination in the same words.
-ACTUAL (2026-08-27): they do NOT. Class summary reads "View your report, available to download in the Reports tab", while Aggregated data reads "View your report, available to download on the Reports page" — "Reports tab" vs "Reports page".</t>
-  </si>
-  <si>
-    <t>Grounded live 2026-08-27, both strings captured verbatim from the same open panel. A low-severity copy inconsistency, raised as a case so it is not rediscovered during automation and so any verbatim-copy assertion is written against the correct string per notification type. Confirm with the product team whether this is intended before raising a ticket. Full failure copy also captured: "Sorry, something went wrong. The &lt;TYPE&gt; report you requested failed to generate. Details available in the Reports tab".</t>
+2. For each report-ready row, read its title and its body line.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every report-ready notification refers to the Reports destination in the same words.
+ACTUAL (2026-09-14): they do NOT. "Your Assignments summary report is ready" reads "…available to download on the Reports page", while "Your Class summary report is ready", "Your Aggregated data report is ready" and "Your Class daily data report is ready" read "…available to download in the Reports tab".</t>
+  </si>
+  <si>
+    <t>**[CORRECTED 2026-09-14 — live pass]** The inconsistency is real but the recorded PAIRING was stale: on 2026-09-14 "on the Reports page" belongs to Assignments summary and Aggregated data reads "in the Reports tab". Assert per notification TYPE, and read the rows present at run time — the five visible rows change as reports are generated. — Superseded note follows: Grounded live 2026-08-27, both strings captured verbatim from the same open panel. A low-severity copy inconsistency, raised as a case so it is not rediscovered during automation and so any verbatim-copy assertion is written against the correct string per notification type. Confirm with the product team whether this is intended before raising a ticket. Full failure copy also captured: "Sorry, something went wrong. The &lt;TYPE&gt; report you requested failed to generate. Details available in the Reports tab".</t>
   </si>
   <si>
     <t>TST_ASHL_TC_3</t>
@@ -479,7 +478,7 @@
 "CLASSES" is the active tab by default, the page heading shows the school name, and the browser tab reads "Classes | Cambridge One".</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. Tab qids "aDetail-1" (Classes), "aDetail-2" (Students), "aDetail-4" (Staff), "aDetail-5" (Library), "aDetail-6" (Reports). ⚠️ "aDetail-3" IS SKIPPED — the sequence is 1,2,4,5,6. Do not iterate 1..5 assuming contiguity. ⚠️ THE ACTIVE MARKER IS ON THE PARENT &lt;li&gt;, not the anchor: "li.nav-item.active &gt; a". The anchor className is identical on every tab whether active or not, so asserting on the link class is a guaranteed false green. Labels render UPPER CASE — confirm whether that is CSS text-transform or the actual text before asserting case-sensitively.</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. Tab qids "aDetail-1" (Classes), "aDetail-2" (Students), "aDetail-4" (Staff), "aDetail-5" (Library), "aDetail-6" (Reports). ⚠️ "aDetail-3" IS SKIPPED — the sequence is 1,2,4,5,6. Do not iterate 1..5 assuming contiguity. ⚠️ THE ACTIVE MARKER IS ON THE PARENT &lt;li&gt;, not the anchor: "li.nav-item.active &gt; a". The anchor className is identical on every tab whether active or not, so asserting on the link class is a guaranteed false green. Labels render UPPER CASE — confirm whether that is CSS text-transform or the actual text before asserting case-sensitively.</t>
   </si>
   <si>
     <t>TST_ASHL_TC_6</t>
@@ -508,7 +507,7 @@
 The school heading stays unchanged throughout.</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27 — all five walked and every URL and title confirmed. ⚠️ NOTE the STUDENTS tab routes to "/learner", NOT "/student". A URL assertion built from the tab label will fail on this one. Tabs carry REAL hrefs (unlike the footer, whose logged-in hrefs collapse to javascript:void(0) — TST_FOOT_TC_10 remarks), so tab navigation is genuinely href-driven. TIMING measured this session: Reports took ~4.3 s to become active, Classes ~1.2 s. Poll for "li.nav-item.active &gt; a" carrying the expected qid rather than using a fixed pause (admin-shared.md §B8).</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27 — all five walked and every URL and title confirmed. ⚠️ NOTE the STUDENTS tab routes to "/learner", NOT "/student". A URL assertion built from the tab label will fail on this one. Tabs carry REAL hrefs (unlike the footer, whose logged-in hrefs collapse to javascript:void(0) — TST_FOOT_TC_10 remarks), so tab navigation is genuinely href-driven. TIMING measured this session: Reports took ~4.3 s to become active, Classes ~1.2 s. Poll for "li.nav-item.active &gt; a" carrying the expected qid rather than using a fixed pause (admin-shared.md §B8).</t>
   </si>
   <si>
     <t>TST_ASHL_TC_7</t>
@@ -528,7 +527,7 @@
 ACTUAL (2026-08-27): this FAILS. No tab link carries aria-current or aria-selected; the only indicator is the "active" CSS class on the parent &lt;li&gt;, which is presentational.</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. This is the SECOND instance of the same gap in this batch — the My Profile tabs have it too (TST_MYPR_TC_8). Worth raising as one combined accessibility ticket rather than two. The school tabs are at least recoverable for automation via "li.nav-item.active"; the profile tabs have no indicator at all, which makes them the more severe of the two.</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. This is the SECOND instance of the same gap in this batch — the My Profile tabs have it too (TST_MYPR_TC_8). Worth raising as one combined accessibility ticket rather than two. The school tabs are at least recoverable for automation via "li.nav-item.active"; the profile tabs have no indicator at all, which makes them the more severe of the two.</t>
   </si>
   <si>
     <t>TST_FOOT_TC_10</t>
@@ -596,7 +595,7 @@
 Two controls are offered: "Continue" and "Cancel".</t>
   </si>
   <si>
-    <t>COPY GROUNDED LIVE 2026-08-27 — captured VERBATIM from the pre-rendered DOM (admin-shared.md §A6) WITHOUT triggering the action, which is the only safe way to verify it on a shared school. Dialog buttons: Continue "adEdit-3", Cancel "adEdit-4". The expected copy is therefore VERIFIED even though the dialog was never opened; only the act of opening it is [ASSUMED].</t>
+    <t>**[CORRECTED 2026-09-14 — live pass]** Opening the warning is now VERIFIED live (KNF-XRD-QVE, 2026-09-14) — the copy matched verbatim. Scope every dialog selector with "#changeSchoolKey" (the Classes tab holds 5 .modal-content). The warning icon is "div.warning-heading &gt; i.fa.fa-exclamation-triangle". Continue and Cancel are anchors. — Superseded note follows: COPY GROUNDED LIVE 2026-08-27 — captured VERBATIM from the pre-rendered DOM (admin-shared.md §A6) WITHOUT triggering the action, which is the only safe way to verify it on a shared school. Dialog buttons: Continue "adEdit-3", Cancel "adEdit-4". The expected copy is therefore VERIFIED even though the dialog was never opened; only the act of opening it is [ASSUMED].</t>
   </si>
   <si>
     <t>TST_SKEY_TC_3</t>
@@ -638,16 +637,22 @@
     <t>Verify the school key is unchanged when the warning dialog is cancelled</t>
   </si>
   <si>
+    <t>Logged in as school-admin &lt;ADMIN_USER&gt; on Thor; school KNF-XRD-QVE ("3 July Test School 2") opened from "My school accounts" — NEVER FCN-CHZ-PDA; Classes tab displayed.</t>
+  </si>
+  <si>
     <t xml:space="preserve">1. Note the current school key.
 2. Open "School settings" and click "Change school key".
 3. Click "Cancel" in the warning dialog.
 4. Re-read the school key.</t>
   </si>
   <si>
-    <t>[ASSUMED] The dialog closes and the school key is UNCHANGED.</t>
-  </si>
-  <si>
-    <t>⚠️ EXPECTED RESULT NOT VERIFIED — the dialog was never opened, by design, on the shared school. This is the SAFE half of the flow and is the one case here that could reasonably be run on a shared school, PROVIDED Cancel is clicked and never Continue. Even so, treat it carefully: a misclick is irreversible. Cancel qid "adEdit-4". Also confirm whether dismissing via Esc or a backdrop click behaves the same as Cancel.</t>
+    <t>School key: KNF-XRD-QVE</t>
+  </si>
+  <si>
+    <t>The dialog closes — the modal is display:none, no .modal-backdrop remains and body.modal-open is removed — and the school key displayed on the Classes tab is UNCHANGED.</t>
+  </si>
+  <si>
+    <t>**[CORRECTED 2026-09-14 — live pass]** DECISION [user, 2026-09-14]: run on KNF-XRD-QVE, never FCN-CHZ-PDA. KEY UNCHANGED is VERIFIED live (before / while open / after all "KNF-XRD-QVE"). "Closed" must be checked with all three signals — the "show" class alone reports closed while the backdrop still covers the page. [ASSUMED] that a REAL click on Cancel closes it: during grounding a SYNTHETIC click on Cancel (a[data-dismiss=modal]) did not, Escape did (fade within 1.5 s), and the grounding browser's real input was not working that day. — Superseded note follows: ⚠️ EXPECTED RESULT NOT VERIFIED — the dialog was never opened, by design, on the shared school. This is the SAFE half of the flow and is the one case here that could reasonably be run on a shared school, PROVIDED Cancel is clicked and never Continue. Even so, treat it carefully: a misclick is irreversible. Cancel qid "adEdit-4". Also confirm whether dismissing via Esc or a backdrop click behaves the same as Cancel.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_32</t>
@@ -700,7 +705,7 @@
 Observed 2026-08-27 for &lt;ADMIN_USER&gt;: 7 schools, numbered 01–07.</t>
   </si>
   <si>
-    <t xml:space="preserve">[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. Card qid "aDashboard-N" (a.inst-link); chevron is a SEPARATE "aDashboard1-N". Both are POSITIONAL. The school key is carried in the card's aria-label, which is what makes key-based selection possible (schoolAdminDashboard.schoolLinkByKey uses a.inst-link[aria-label*="{{key}}"]).
+    <t xml:space="preserve">**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. Card qid "aDashboard-N" (a.inst-link); chevron is a SEPARATE "aDashboard1-N". Both are POSITIONAL. The school key is carried in the card's aria-label, which is what makes key-based selection possible (schoolAdminDashboard.schoolLinkByKey uses a.inst-link[aria-label*="{{key}}"]).
 ⚠️ NEVER assert the literal count 7 — this is a shared account and the list changes (admin-shared.md §A5). Assert the card STRUCTURE and that the expected key is present.
 Extends the existing SADB module (TST_SADB_TC_1 opens a school by key) — that case already covers opening; this one covers the LISTING, which nothing did.
 ⚠️ EXTENDS admin-shared.md §0, which documents 4 schools. This account sees 7 — KNF-XRD-QVE, HQC-ZWM-ZVF and GYB-JMU-KYA were undocumented.</t>
@@ -718,14 +723,13 @@
 4. Compare the Classes listings of the two.</t>
   </si>
   <si>
-    <t>Schools: &lt;SCHOOL_KEY_A&gt; and &lt;SCHOOL_KEY_B&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each school opens under its own org slug, /admin/admin/org_&lt;slug&gt;/class, with its own name as the page heading and its own class list. No content from the previously opened school persists.
-Observed 2026-08-27: "3 July Test School 1" (FCN-CHZ-PDA) opened as org_perf_testschool_1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GROUNDED PARTIALLY 2026-08-27 — one school was opened and its slug confirmed; the SWITCH between two schools was not exercised, so step 4 is [ASSUMED].
+    <t>Schools: FCN-CHZ-PDA ("3 July Test School 1") and KNF-XRD-QVE ("3 July Test School 2")</t>
+  </si>
+  <si>
+    <t>Each school opens under its own org slug with its own heading and its own school key: FCN-CHZ-PDA → /admin/admin/org_perf_testschool_1/class, "3 July Test School 1"; KNF-XRD-QVE → /admin/admin/org_perf_testschool_2/class, "3 July Test School 2". No content from the previously opened school persists — e.g. the FCN-only fixture class "Fixture_GradeSettings_DO_NOT_DELETE" is absent from KNF-XRD-QVE.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**[CORRECTED 2026-09-14 — live pass]** Step 4 VERIFIED live 2026-09-14 by switching FCN-CHZ-PDA → KNF-XRD-QVE. The fixture-class absence is a falsifiable no-carry-over check; never assert class COUNTS (both schools are shared and mutable). — Superseded note follows: GROUNDED PARTIALLY 2026-08-27 — one school was opened and its slug confirmed; the SWITCH between two schools was not exercised, so step 4 is [ASSUMED].
 ⚠️ The org slug is NOT derivable from the school name or key — "3 July Test School 1" (FCN-CHZ-PDA) maps to org_perf_testschool_1. Capture each slug; never construct it.
 The school context MUST be set by clicking the card — deep-linking /admin/admin/org_&lt;slug&gt;/class returns /dashboard/error even when authenticated (admin-shared.md §A1).
 Worth checking whether the per-account server-side class Filter and Search (§A4) are scoped per school or leak across organisations — that is unknown and would be a real defect if they leak.</t>
@@ -751,7 +755,7 @@
     <t>Both cards show the SAME display name but DIFFERENT school keys, and the card selected by key opens that specific school.</t>
   </si>
   <si>
-    <t xml:space="preserve">[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27 — cards 01 and 02 both read "3 July Test School 1" with keys FCN-CHZ-PDA and ZPB-TWP-AEQ, and identical addresses too.
+    <t xml:space="preserve">**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27 — cards 01 and 02 both read "3 July Test School 1" with keys FCN-CHZ-PDA and ZPB-TWP-AEQ, and identical addresses too.
 ⚠️ THIS IS THE CASE THAT JUSTIFIES admin-shared.md §0's standing rule: ALWAYS select a school by KEY, never by name or card position. Selecting by name is ambiguous here, and card qids (aDashboard-N) are positional so they re-issue when the list changes.
 Confirming WHICH school loaded (step 3) needs a distinguishing feature — the org slug in the URL is the reliable one, since the heading shows the shared name.</t>
   </si>
@@ -791,7 +795,7 @@
     <t>Verify each wizard step blocks progress until its required input is supplied</t>
   </si>
   <si>
-    <t>The "Set up a school account" wizard is open at step 2 (School type).</t>
+    <t>Logged in as school-admin &lt;ADMIN_USER&gt; on Thor; the "Set up a school account" wizard (/dashboard/teacher/setupschool) open at School type.</t>
   </si>
   <si>
     <t xml:space="preserve">1. On School type, without selecting an option, attempt to continue.
@@ -799,10 +803,16 @@
 3. Repeat the same check for Number of teachers, School name, School location, School address and School contact details.</t>
   </si>
   <si>
-    <t>[ASSUMED] On each step the Next control is unavailable until that step's required input is supplied, and becomes available once it is. No step can be skipped.</t>
-  </si>
-  <si>
-    <t>⚠️ EXPECTED RESULT NOT VERIFIED — the wizard was not walked in this session. INFERRED from the existing automation, whose case titles state the enabling direction only, e.g. TST_SCTY_TC_3 "Select first radio option (Primary school) to ENABLE Next button" and TST_SNAM_TC_3 "Fill school name field to ENABLE Next button". The DISABLED half is nowhere asserted, which is the gap this case fills. Confirm whether Next is natively disabled or only CSS-disabled — admin-shared.md §B4 records CSS-only disabling elsewhere in this app, which would make a naive enabled-state check a false green. SIDE-EFFECT FREE: stops short of submission.</t>
+    <t xml:space="preserve">On every step the Next button is NATIVELY disabled until that step is valid, then enabled:
+School type / Number of teachers — until an option is selected.
+School name — until non-whitespace text is entered.
+Location — arrives pre-filled from the account; clearing it, whitespace, or a partial value ("Ind") disables Next.
+Address — Street address AND City / town are both required; Region and Postal code are optional.
+Telephone — telephone code AND a numeric telephone number are required; the website URL is optional but a malformed one ("example") disables Next.
+No step shows an inline error; the disabled Next is the only signal. The summary is reached; "Send Request" is NOT clicked.</t>
+  </si>
+  <si>
+    <t>**[CORRECTED 2026-09-14 — live pass]** VERIFIED LIVE 2026-09-14 — walked to the summary, never submitted. Next is NATIVELY disabled (disabled attribute + .disabled + pointer-events none), so an isEnabled assertion is valid. The wizard advances IN-PAGE (URL never changes) and the Next qid differs per step. ⚠️ The existing wizard modules' generic "button.btn-purple" also matches "Send Request" (t-ss-as-btn-1) — stop by qid. The summary omits school type and number of teachers. — Superseded note follows: ⚠️ EXPECTED RESULT NOT VERIFIED — the wizard was not walked in this session. INFERRED from the existing automation, whose case titles state the enabling direction only, e.g. TST_SCTY_TC_3 "Select first radio option (Primary school) to ENABLE Next button" and TST_SNAM_TC_3 "Fill school name field to ENABLE Next button". The DISABLED half is nowhere asserted, which is the gap this case fills. Confirm whether Next is natively disabled or only CSS-disabled — admin-shared.md §B4 records CSS-only disabling elsewhere in this app, which would make a naive enabled-state check a false green. SIDE-EFFECT FREE: stops short of submission.</t>
   </si>
   <si>
     <t>TST_ASHL_TC_8</t>
@@ -821,7 +831,7 @@
     <t>On every tab, no dialog, warning or error is visible on load. The screen shows only its own content.</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27 — verified that every dialog present in the DOM was hidden on load (Classes 5, Students 4, Staff 1; all offsetParent === null). ⚠️ THIS IS THE HEADLINE AUTOMATION TRAP FOR THIS SCENARIO. Admin dialogs are PRE-RENDERED, so they exist in the DOM before anything triggers them. Any check of the form "getElementCount(dialog) &gt; 0" therefore passes ALWAYS and proves nothing — admin-shared.md §B2 records this silently breaking reset_filters for weeks. Assert VISIBILITY, never presence. Note also that opacity:0 still counts as visible to Playwright; only display:none is hidden.</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27 — verified that every dialog present in the DOM was hidden on load (Classes 5, Students 4, Staff 1; all offsetParent === null). ⚠️ THIS IS THE HEADLINE AUTOMATION TRAP FOR THIS SCENARIO. Admin dialogs are PRE-RENDERED, so they exist in the DOM before anything triggers them. Any check of the form "getElementCount(dialog) &gt; 0" therefore passes ALWAYS and proves nothing — admin-shared.md §B2 records this silently breaking reset_filters for weeks. Assert VISIBILITY, never presence. Note also that opacity:0 still counts as visible to Playwright; only display:none is hidden.</t>
   </si>
   <si>
     <t>TST_ASHL_TC_9</t>
@@ -841,7 +851,7 @@
 Both offer a "Close" control.</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. COPY GROUNDED LIVE 2026-08-27 — both captured VERBATIM from the pre-rendered DOM (§A6) without reaching the capped state, which would otherwise require 51+ rows. Note the VERB differs with the domain — "delete" for classes, "remove" for students — so a single shared assertion string is wrong. The LIMIT (50) and the sentence shape are the consistent parts. Reaching these states for real is Blocked on the shared school (admin-shared.md §A5: it holds 26 students, so the 50-student cap cannot be hit).</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. COPY GROUNDED LIVE 2026-08-27 — both captured VERBATIM from the pre-rendered DOM (§A6) without reaching the capped state, which would otherwise require 51+ rows. Note the VERB differs with the domain — "delete" for classes, "remove" for students — so a single shared assertion string is wrong. The LIMIT (50) and the sentence shape are the consistent parts. Reaching these states for real is Blocked on the shared school (admin-shared.md §A5: it holds 26 students, so the 50-student cap cannot be hit).</t>
   </si>
   <si>
     <t>TST_ASHL_TC_10</t>
@@ -862,7 +872,7 @@
 Change school key — "CAREFUL!" / "Changing the school key cannot be undone" / "Cancel"</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. ALL THREE CAPTURED VERBATIM 2026-08-27 from the pre-rendered DOM, without triggering any of them — which is the only safe way, since all three are destructive on a shared school. ⚠️ The change-school-key dialog is present on EVERY admin tab (Classes, Students, Staff all carry it) because School settings lives in the shared page chrome — scope any modal selector with :has(...) to the specific dialog, or it will match this one everywhere. Async follow-ups are also pre-rendered and worth checking in the same pass: "This will take a few minutes" (classes) and "Removing students may take some time" (students).</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. ALL THREE CAPTURED VERBATIM 2026-08-27 from the pre-rendered DOM, without triggering any of them — which is the only safe way, since all three are destructive on a shared school. ⚠️ The change-school-key dialog is present on EVERY admin tab (Classes, Students, Staff all carry it) because School settings lives in the shared page chrome — scope any modal selector with :has(...) to the specific dialog, or it will match this one everywhere. Async follow-ups are also pre-rendered and worth checking in the same pass: "This will take a few minutes" (classes) and "Removing students may take some time" (students).</t>
   </si>
   <si>
     <t>TST_SADB_TC_5</t>
@@ -881,11 +891,11 @@
 5. Confirm the administrator view is restored.</t>
   </si>
   <si>
-    <t xml:space="preserve">After step 2 the browser navigates to /dashboard/teacher/dashboard, the browser tab reads "Teacher dashboard | Cambridge One", the page greets the user ("Hi &lt;FIRST_NAME&gt;!") and the toggle now reports "Teacher currently active".
-After step 4 the browser returns to /admin/admin/dashboard, titled "My school accounts | Cambridge One", and the toggle reports "Administrator currently active".</t>
-  </si>
-  <si>
-    <t>GROUNDED LIVE 2026-08-27 — the full round trip was performed and the account was left in Administrator view. ⚠️ THE SWITCH ELEMENT IS NAMED DIFFERENTLY IN EACH VIEW: ".can-toggle__switch" (double underscore) in the admin view, ".can-toggle-switch" (single hyphen) in the teacher view. A selector written for one view SILENTLY FAILS to find it in the other, which breaks exactly the round trip this case exercises. Use "#teacher-admin-toggle" (stable in both) and read the input's checked state — false = Administrator, true = Teacher. The focusable control is the inner [tabindex="0"] div; the input itself is aria-hidden. The toggle also appears on inner admin tabs, not just the dashboard. Existing selector schoolAdminDashboard.teacherAdminToggle already targets the input; this extends SADB. SIDE-EFFECT FREE — a view switch only.</t>
+    <t xml:space="preserve">After step 2 the browser navigates to /dashboard/teacher/dashboard, the page greets the user ("Hi &lt;FIRST_NAME&gt;!"), #teacher-admin-toggle is checked and the switch's accessible name reports "Teacher currently active".
+After step 4 the browser returns to the ADMIN PAGE THE TOGGLE WAS LEFT FROM — /admin/admin/dashboard when started there — #teacher-admin-toggle is unchecked and the accessible name reports "Administrator currently active".</t>
+  </si>
+  <si>
+    <t>**[CORRECTED 2026-09-14 — live pass]** Toggling back returns to the admin page the round trip STARTED on (verified from /class on 2026-09-14), so start this case on the dashboard. Do NOT assert the document title — it varies with the load path ("Administrator | Cambridge One" vs "My school accounts | Cambridge One"). — Superseded note follows: GROUNDED LIVE 2026-08-27 — the full round trip was performed and the account was left in Administrator view. ⚠️ THE SWITCH ELEMENT IS NAMED DIFFERENTLY IN EACH VIEW: ".can-toggle__switch" (double underscore) in the admin view, ".can-toggle-switch" (single hyphen) in the teacher view. A selector written for one view SILENTLY FAILS to find it in the other, which breaks exactly the round trip this case exercises. Use "#teacher-admin-toggle" (stable in both) and read the input's checked state — false = Administrator, true = Teacher. The focusable control is the inner [tabindex="0"] div; the input itself is aria-hidden. The toggle also appears on inner admin tabs, not just the dashboard. Existing selector schoolAdminDashboard.teacherAdminToggle already targets the input; this extends SADB. SIDE-EFFECT FREE — a view switch only.</t>
   </si>
   <si>
     <t>TST_SADB_TC_6</t>
@@ -907,7 +917,7 @@
 Observed 2026-08-27: administrator view 7 schools; teacher view 8 school groups, including "ABERYSTWYTH COLLEGE : THOR" and "LTI INTEGRATIONS TEST2", neither of which appears in the administrator list.</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. This matters because it is easy to assume the two views show the same estate — they do not, and a test asserting equal school counts across the toggle will fail. ⚠️ The teacher view groups by school DISPLAY NAME, so the two distinct schools both called "3 July Test School 1" (FCN-CHZ-PDA and ZPB-TWP-AEQ) collapse into a SINGLE group there. The admin view keeps them separate via their keys. Do not match schools across the two views by name. ⚠️ NEVER assert the literal counts 7 and 8 — shared account (§A5). Assert the RELATIONSHIP: the teacher list contains at least one school the admin list does not. ⚠️ Every "Create class" button in the teacher view shares qid "tDashboard-ncls-btn-1" — 7 elements, one per school group. See TST_SADB_TC_7.</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. This matters because it is easy to assume the two views show the same estate — they do not, and a test asserting equal school counts across the toggle will fail. ⚠️ The teacher view groups by school DISPLAY NAME, so the two distinct schools both called "3 July Test School 1" (FCN-CHZ-PDA and ZPB-TWP-AEQ) collapse into a SINGLE group there. The admin view keeps them separate via their keys. Do not match schools across the two views by name. ⚠️ NEVER assert the literal counts 7 and 8 — shared account (§A5). Assert the RELATIONSHIP: the teacher list contains at least one school the admin list does not. ⚠️ Every "Create class" button in the teacher view shares qid "tDashboard-ncls-btn-1" — 7 elements, one per school group. See TST_SADB_TC_7.</t>
   </si>
   <si>
     <t>TST_SADB_TC_7</t>
@@ -930,13 +940,13 @@
 6. Search for the class by name.</t>
   </si>
   <si>
-    <t>School: &lt;SCHOOL_KEY&gt; · Class name: "AutoClass_TeacherView_&lt;RUN_ID&gt;"</t>
+    <t>School: KNF-XRD-QVE ("3 July Test School 2") · Class name: "AutoClass_TeacherView_&lt;RUN_ID&gt;"</t>
   </si>
   <si>
     <t>[ASSUMED] The class is created under the chosen school and, after step 6, is listed in that school's Admin Classes tab under the same name.</t>
   </si>
   <si>
-    <t xml:space="preserve">⚠️ CREATES REAL DATA — a real class on a real school. This decides suite placement absolutely: it must NOT sit in a side-effect-free suite. Use the sweepable "AutoClass_" prefix (admin-shared.md §A7) so leftovers are recognisable, and note that class DELETE is SOFT, so every run leaves a permanent soft-deleted row (§A5).
+    <t xml:space="preserve">**[CORRECTED 2026-09-14 — live pass]** DECISION [user, 2026-09-14]: run on KNF-XRD-QVE in its OWN data-owning suite — never in the read-only Generic suite. Sweep AutoClass_TeacherView_ leftovers on KNF before creating; delete the created class by its URL afterwards. The school's name is unique in the teacher view. — Superseded note follows: ⚠️ CREATES REAL DATA — a real class on a real school. This decides suite placement absolutely: it must NOT sit in a side-effect-free suite. Use the sweepable "AutoClass_" prefix (admin-shared.md §A7) so leftovers are recognisable, and note that class DELETE is SOFT, so every run leaves a permanent soft-deleted row (§A5).
 ⚠️ CHOOSING THE RIGHT "Create class" IS THE HARD PART. All 7 buttons in the teacher view share qid "tDashboard-ncls-btn-1", one per school group, and the qid cannot distinguish them. The button must be located THROUGH its school-group heading, or the class lands on the wrong school. A class literally named "admin as a teacher class" already exists under MQA Sierra School, suggesting this has been done manually before.
 ⚠️ CLASS CREATION IS ASYNCHRONOUS (§A4) — the success dialog says it "can take up to 12 hours"; measured visibility ~24 s on a responsive Thor and &gt;90 s on a loaded one. Step 6 must POLL, and the active-class count does NOT increment immediately, so never assert count + 1.
 Teacher-side creation itself is already automated (ENTE / CREA modules, createNewClass.page.js) — what is NOT covered anywhere is this CROSS-ROLE journey, which is the point of the case.
@@ -949,22 +959,23 @@
     <t>Verify clicking a notification opens its target and clears it from the unread count</t>
   </si>
   <si>
-    <t>#3 - Verify notifications</t>
-  </si>
-  <si>
     <t>Signed in as an administrator with at least one unread notification, the bell showing a count.</t>
   </si>
   <si>
-    <t>1. Record the unread badge count. 2. Open the notifications panel. 3. Click a notification whose target is known (e.g. a report-ready notification). 4. Confirm where it lands. 5. Re-open the panel and re-read the badge count and the item's read state.</t>
+    <t xml:space="preserve">1. Record the unread count from the bell's accessible name.
+2. Open the notifications panel.
+3. Click the OLDEST visible report-ready notification.
+4. Confirm where it lands.
+5. Re-read the unread count.</t>
   </si>
   <si>
     <t>An account with unread notifications; a report-ready notification if available.</t>
   </si>
   <si>
-    <t>The click navigates to the notification's target (a report-ready notification lands on the Reports tab), the item is marked read, and the unread badge count decreases by one. [ASSUMED]</t>
-  </si>
-  <si>
-    <t>Added 2026-09-01 from the other team's TC_GEN_003, whose steps click a notification and mark it read. All five of our notification cases (TST_INVI_TC_7-TC_11) are about rendering - badge, grouping, dates, wording - and none clicks a row. TST_INVI_TC_7 already pairs the badge with its accessible name, so this closes the loop by proving the count actually changes. Mutates state (read status is not reversible) - keep out of side-effect-free suites.</t>
+    <t>The click navigates to the notification's target (a report-ready notification lands on the Reports tab), the item is marked read, and the unread badge count decreases by one. `[ASSUMED]`</t>
+  </si>
+  <si>
+    <t>**[CORRECTED 2026-09-14 — live pass]** DECISION [user, 2026-09-14]: run on &lt;ADMIN_USER&gt; and accept consuming one unread notification per run (93 unread ≈ 90 runs); click the OLDEST visible report-ready row. Read the count before and after in the same run — never an absolute number. The landing destination is still [ASSUMED] (not grounded, because a click cannot be undone). — Superseded note follows: Added 2026-09-01 from the other team's TC_GEN_003, whose steps click a notification and mark it read. All five of our notification cases (`TST_INVI_TC_7`–`TC_11`) are about **rendering** — badge, grouping, dates, wording — and none clicks a row. `TST_INVI_TC_7` already pairs the badge with its accessible name, so this closes the loop by proving the count actually changes. **Mutates state** (read status is not reversible) — keep out of side-effect-free suites.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_34</t>
@@ -973,25 +984,22 @@
     <t>Verify an MQA administrator does see the MQA/CQA restricted products</t>
   </si>
   <si>
-    <t>#5 - Verify non mqa admin should not see cqa/mqa product</t>
-  </si>
-  <si>
     <t>An MQA-provisioned administrator account with access to a school holding MQA/CQA products.</t>
   </si>
   <si>
     <t>1. Sign in as the MQA-provisioned administrator. 2. Open the school's Library tab. 3. Search for the restricted product by title and confirm it is listed.</t>
   </si>
   <si>
-    <t>MQA admin &lt;MQA_ADMIN_ACCOUNT&gt;; restricted product &lt;MQA_RESTRICTED_PRODUCT&gt;.</t>
-  </si>
-  <si>
-    <t>The MQA/CQA product is listed for the MQA administrator. [ASSUMED]</t>
-  </si>
-  <si>
-    <t>Added 2026-09-01 from the other team's TC_GEN_005, whose step 3 is an explicit control check. TST_LIBR_TC_32 proves only the negative half - that restricted products are hidden from a non-MQA admin - which a defect hiding the product from everyone would also satisfy. The pair is what makes either half meaningful. This is the same structural point as TST_CLST_TC_24 on the Classes tab: a negative-only assertion cannot distinguish correct behaviour from over-blocking.</t>
-  </si>
-  <si>
-    <t>Blocked at design time (skill rule 4): needs an MQA-provisioned administrator account, the counterpart to the non-MQA account TST_LIBR_TC_32 is already waiting on. Unblock both together - one fixture request covers the pair.</t>
+    <t>MQA admin `&lt;MQA_ADMIN_ACCOUNT&gt;`; restricted product `&lt;MQA_RESTRICTED_PRODUCT&gt;`.</t>
+  </si>
+  <si>
+    <t>The MQA/CQA product **is** listed for the MQA administrator. `[ASSUMED]`</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_GEN_005, whose step 3 is an explicit control check. `TST_LIBR_TC_32` proves only the negative half — that restricted products are hidden from a non-MQA admin — which a defect hiding the product from **everyone** would also satisfy. The pair is what makes either half meaningful. This is the same structural point as `TST_CLST_TC_24` on the Classes tab: a negative-only assertion cannot distinguish correct behaviour from over-blocking.</t>
+  </si>
+  <si>
+    <t>Blocked at design time (skill rule 4): needs an MQA-provisioned administrator account, the counterpart to the non-MQA account `TST_LIBR_TC_32` is already waiting on. Unblock both together — one fixture request covers the pair.</t>
   </si>
   <si>
     <t>TST_FOOT_TC_11</t>
@@ -1000,22 +1008,20 @@
     <t>Verify every admin footer link opens its intended destination</t>
   </si>
   <si>
-    <t>#8 - Verify footer link</t>
-  </si>
-  <si>
     <t>On any admin page with the footer visible.</t>
   </si>
   <si>
-    <t>1. Scroll to the footer and record every link it renders. 2. Click each link in turn. 3. Confirm the destination that opens and return. 4. Reconcile the set of links found against TST_FOOT_TC_10.</t>
-  </si>
-  <si>
-    <t>The footer links - the other team name Terms of use, Privacy notice, Accessibility, Our approach and FAQs.</t>
-  </si>
-  <si>
-    <t>Each footer link opens its intended destination and none is broken (no 404, no dead anchor). [ASSUMED]</t>
-  </si>
-  <si>
-    <t>Added 2026-09-01 from the other team's TC_GEN_008, which clicks each link and checks the destination. TST_FOOT_TC_10 asserts the footer renders seven links and omits Site Feedback - a presence check, not a navigation check. Reconcile the count while grounding: our register says seven links, theirs names five. One of the two is wrong; correct whichever it is and note the outcome here. Read-only, but links may open new tabs or external sites - handle that in automation.</t>
+    <t>1. Scroll to the footer and record every link it renders. 2. Click each link in turn. 3. Confirm the destination that opens and return. 4. Reconcile the set of links found against `TST_FOOT_TC_10`.</t>
+  </si>
+  <si>
+    <t>Admin footer links (7): Terms of use · Privacy notice · Accessibility · Our approach · FAQs · Cambridge One for schools · Help</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each internal footer link opens its page with no 404: Terms of use → /terms ("Terms of use"), Privacy notice → /privacy ("Privacy Notice"), Accessibility → /accessibility ("Accessibility on Cambridge One"), Cambridge One for schools → /institution-request.
+FAQs and Help both lead to the external help centre, and Our approach opens http://www.cambridge.org/english in a new tab.</t>
+  </si>
+  <si>
+    <t>**[CORRECTED 2026-09-14 — live pass]** Count RECONCILED: the admin footer renders SEVEN links — our register was right; the other team's five-link list is incomplete. Internal destinations VERIFIED live 2026-09-14. FAQs and Help point to the SAME external URL (a *helptest* host on Thor — environment-specific). "Our approach" has rel="nopener" — MISSPELT (should be noopener) — a minor security-hygiene defect. Logged-in internal hrefs are javascript:void(0): assert the resulting URL, never the href. — Superseded note follows: Added 2026-09-01 from the other team's TC_GEN_008, which clicks each link and checks the destination. `TST_FOOT_TC_10` asserts the footer **renders seven links and omits Site Feedback** — a presence check, not a navigation check. **Reconcile the count while grounding:** our register says seven links, theirs names five. One of the two is wrong; correct whichever it is and note the outcome here. **Read-only**, but links may open new tabs or external sites — handle that in automation.</t>
   </si>
   <si>
     <t>TST_SADB_TC_8</t>
@@ -1024,25 +1030,22 @@
     <t>Verify data stays scoped to the active organisation when an admin manages several schools</t>
   </si>
   <si>
-    <t>#11 - Verify different tab navigation</t>
-  </si>
-  <si>
-    <t>An administrator with access to two or more schools, where each school holds at least one record (class, student, staff member, library product) that exists only in that school.</t>
-  </si>
-  <si>
-    <t>1. Sign in as the multi-org administrator and open school A. 2. On each tab - Classes, Students, Staff, Library - confirm every listed record belongs to school A, and specifically that school B's unique records are absent. 3. Switch to school B and repeat in the opposite direction. 4. Apply a search or filter in school A, then switch to school B, and confirm no results carry across.</t>
-  </si>
-  <si>
-    <t>Multi-org admin &lt;MULTI_ORG_ADMIN&gt;; unique records &lt;A_ONLY_RECORD&gt; and &lt;B_ONLY_RECORD&gt;.</t>
-  </si>
-  <si>
-    <t>Every tab shows only the active organisation's data. No record unique to the other school appears anywhere, and switching organisations does not carry search or filter results across. [ASSUMED]</t>
-  </si>
-  <si>
-    <t>Added 2026-09-01 from the other team's TC_ORG_001, whose expected result ends "with no cross-org data leakage". TST_SADB_TC_3 proves each organisation loads independently; it does not prove one cannot see the other's data. Highest-severity gap of the entire comparison - a leak here is a data-privacy incident, not a UI defect, which is why this is High priority despite sitting in a thinly covered area. Step 4 exists because carried-over query state is the most likely mechanism for a leak.</t>
-  </si>
-  <si>
-    <t>Blocked at design time (skill rule 4): needs a multi-organisation admin fixture with records unique to each school, so that absence is provable rather than assumed. Unblock by provisioning two small schools under one admin with deliberately distinct data. NOTE: the multi-organisation area has no register of its own - if it grows beyond the SADB cases it should get one (see the 2026-09-01 handoff).</t>
+    <t>An administrator with access to two or more schools, where each school holds at least one record (class, student, staff member, library product) that exists **only** in that school.</t>
+  </si>
+  <si>
+    <t>1. Sign in as the multi-org administrator and open school A. 2. On each tab — Classes, Students, Staff, Library — confirm every listed record belongs to school A, and specifically that school B's unique records are **absent**. 3. Switch to school B and repeat in the opposite direction. 4. Apply a search or filter in school A, then switch to school B, and confirm no results carry across.</t>
+  </si>
+  <si>
+    <t>Multi-org admin `&lt;MULTI_ORG_ADMIN&gt;`; unique records `&lt;A_ONLY_RECORD&gt;` and `&lt;B_ONLY_RECORD&gt;`.</t>
+  </si>
+  <si>
+    <t>Every tab shows only the active organisation's data. No record unique to the other school appears anywhere, and switching organisations does not carry search or filter results across. `[ASSUMED]`</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_ORG_001, whose expected result ends "with no cross-org data leakage". `TST_SADB_TC_3` proves each organisation **loads** independently; it does not prove one cannot see the other's data. **Highest-severity gap of the entire comparison** — a leak here is a data-privacy incident, not a UI defect, which is why this is High priority despite sitting in a thinly covered area. Step 4 exists because carried-over query state is the most likely mechanism for a leak.</t>
+  </si>
+  <si>
+    <t>Blocked at design time (skill rule 4): needs a multi-organisation admin fixture with records unique to each school, so that absence is provable rather than assumed. Unblock by provisioning two small schools under one admin with deliberately distinct data. NOTE: the multi-organisation area has no register of its own — if it grows beyond the SADB cases it should get one (see the 2026-09-01 handoff).</t>
   </si>
 </sst>
 </file>
@@ -2572,19 +2575,19 @@
         <v>18</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>21</v>
+        <v>176</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>24</v>
@@ -2601,13 +2604,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>67</v>
@@ -2616,19 +2619,19 @@
         <v>18</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>24</v>
@@ -2637,7 +2640,7 @@
         <v>170</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2645,13 +2648,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>17</v>
@@ -2663,16 +2666,16 @@
         <v>19</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>24</v>
@@ -2689,13 +2692,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>17</v>
@@ -2707,16 +2710,16 @@
         <v>19</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>24</v>
@@ -2733,13 +2736,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>59</v>
@@ -2751,16 +2754,16 @@
         <v>19</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>24</v>
@@ -2777,13 +2780,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>17</v>
@@ -2792,19 +2795,19 @@
         <v>18</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>24</v>
@@ -2813,7 +2816,7 @@
         <v>170</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="32" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2821,13 +2824,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>67</v>
@@ -2836,19 +2839,19 @@
         <v>52</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>24</v>
@@ -2865,13 +2868,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>67</v>
@@ -2883,16 +2886,16 @@
         <v>154</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>24</v>
@@ -2909,13 +2912,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>59</v>
@@ -2927,16 +2930,16 @@
         <v>154</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>24</v>
@@ -2953,13 +2956,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>17</v>
@@ -2971,16 +2974,16 @@
         <v>154</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>24</v>
@@ -2997,13 +3000,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>17</v>
@@ -3015,16 +3018,16 @@
         <v>19</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>24</v>
@@ -3041,13 +3044,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>59</v>
@@ -3056,19 +3059,19 @@
         <v>18</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>24</v>
@@ -3085,13 +3088,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>17</v>
@@ -3100,19 +3103,19 @@
         <v>18</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>24</v>
@@ -3129,13 +3132,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>258</v>
+        <v>86</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>17</v>
@@ -3144,19 +3147,19 @@
         <v>52</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>24</v>
@@ -3173,13 +3176,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>266</v>
+        <v>181</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>17</v>
@@ -3223,7 +3226,7 @@
         <v>274</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>275</v>
+        <v>147</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>17</v>
@@ -3232,19 +3235,19 @@
         <v>109</v>
       </c>
       <c r="G41" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="H41" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="H41" s="2" t="s">
+      <c r="I41" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="I41" s="2" t="s">
+      <c r="J41" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="J41" s="2" t="s">
+      <c r="K41" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>280</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>24</v>
@@ -3261,13 +3264,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>282</v>
-      </c>
       <c r="D42" s="2" t="s">
-        <v>283</v>
+        <v>127</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>67</v>
@@ -3276,19 +3279,19 @@
         <v>18</v>
       </c>
       <c r="G42" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="I42" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="H42" s="2" t="s">
+      <c r="J42" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="I42" s="2" t="s">
+      <c r="K42" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>288</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>24</v>
@@ -3297,11 +3300,11 @@
         <v>170</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Generic/AdminApp_Generic_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Generic/AdminApp_Generic_test_cases.xlsx
@@ -114,7 +114,7 @@
 After step 5 the page RELOADS and returns to English (html lang "en").</t>
   </si>
   <si>
-    <t>**[CORRECTED 2026-09-14 — live pass]** GROUNDED LIVE 2026-09-14 on KNF-XRD-QVE (approved by the user). Persistence is PER-BROWSER, not per-account — a fresh browser context starts in English, so other suites are not affected. es→en reloads the page while en→es does not — the restore step must wait for a navigation. I18N DEFECTS found: footer "Our approach" is not translated; the bell's aria-label stays "Notifications (N unread notifications)"; tab "Clases (10)" has a space before the count while the other tabs do not. "Pautas del centro educativo" (≈ guidelines) is a questionable translation — confirm with product. — Superseded note follows: ⚠️ NOT GROUNDED — no admin-app Spanish copy has been verified. GENUINE GAP: appLangES.json exists but contains only "landing" and "login" sections — it has NO admin-app or footer entries, so the strings this case needs do not exist yet anywhere. When captured they should be added to appLangES.json under a new admin section, matching the existing appLangEN.json pattern. Whether the choice persists per-account server-side (as the class Filter and Search do, admin-shared.md §A4) or only for the session is specifically unknown. CHANGES ACCOUNT STATE: switches the language and must switch it back (step 5).</t>
+    <t>**[CORRECTED 2026-09-14 — live pass]** GROUNDED LIVE 2026-09-14 on KNF-XRD-QVE (approved by the user). Persistence is PER-BROWSER, not per-account — a fresh browser context starts in English, so other suites are not affected. es→en reloads the page while en→es does not — the restore step must wait for a navigation. I18N DEFECTS found: footer "Our approach" is not translated; the bell's aria-label stays "Notifications (N unread notifications)". [CORRECTED 2026-09-15] The earlier claim that tab "Clases (10)" has a space before the count while the other tabs do not is WRONG — a live read found all five Spanish tabs share one format (label and count on separate lines: CLASES (10) · ALUMNOS (15) · PERSONAL (12) · BIBLIOTECA (974) · INFORMES (0)). Not a defect. "Pautas del centro educativo" (≈ guidelines) is a questionable translation — confirm with product. — Superseded note follows: ⚠️ NOT GROUNDED — no admin-app Spanish copy has been verified. GENUINE GAP: appLangES.json exists but contains only "landing" and "login" sections — it has NO admin-app or footer entries, so the strings this case needs do not exist yet anywhere. When captured they should be added to appLangES.json under a new admin section, matching the existing appLangEN.json pattern. Whether the choice persists per-account server-side (as the class Filter and Search do, admin-shared.md §A4) or only for the session is specifically unknown. CHANGES ACCOUNT STATE: switches the language and must switch it back (step 5).</t>
   </si>
   <si>
     <t>TST_MYPR_TC_1</t>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Generic/AdminApp_Generic_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Generic/AdminApp_Generic_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="300">
   <si>
     <t>S.No.</t>
   </si>
@@ -53,6 +53,12 @@
   </si>
   <si>
     <t>Comments / Defect ID</t>
+  </si>
+  <si>
+    <t>Automation Status</t>
+  </si>
+  <si>
+    <t>Automation Evidence</t>
   </si>
   <si>
     <t>TST_ASHL_TC_1</t>
@@ -90,7 +96,13 @@
     <t/>
   </si>
   <si>
-    <t>Not Run</t>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Automated</t>
+  </si>
+  <si>
+    <t>Suite: adminGeneric | 2026-09-16: Pass across 2 runs</t>
   </si>
   <si>
     <t>TST_ASHL_TC_2</t>
@@ -235,6 +247,15 @@
   </si>
   <si>
     <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED PARTIALLY 2026-08-27: the ABSENCE of a limit is verified — ALL SEVEN fields across both tabs have maxlength=null and none is marked required. What the SERVER does is [ASSUMED]. This is a deliberate departure from the rest of the admin app, where limits are declared and enforced client-side (class name 50, grading scale title 20 — admin-shared.md §A3). Because nothing is declared here, boundary cases CANNOT be derived from the markup and must be found by submitting. ⚠️ DO NOT RUN ON &lt;ADMIN_USER&gt; — that account is the login for the whole admin suite. Blocked until a disposable account exists.</t>
+  </si>
+  <si>
+    <t>Not Run</t>
+  </si>
+  <si>
+    <t>Excluded - Phase 1</t>
+  </si>
+  <si>
+    <t>Out of Phase 1 automation scope.</t>
   </si>
   <si>
     <t>TST_MYPR_TC_6</t>
@@ -631,6 +652,9 @@
     <t>BLOCKED at design time 2026-08-27 — IRREVERSIBLE ACTION ON A SHARED SCHOOL. The product itself states "Changing the school key cannot be undone". Unblock with a DEDICATED, DISPOSABLE school that no suite depends on.</t>
   </si>
   <si>
+    <t>BLOCKED - see Comments for the blocker and its unblock route</t>
+  </si>
+  <si>
     <t>TST_SKEY_TC_4</t>
   </si>
   <si>
@@ -953,6 +977,12 @@
 The teacher view groups by display name, so a school with a duplicate name is ambiguous here — pick a school with a UNIQUE name (§A5, TST_SADB_TC_6).</t>
   </si>
   <si>
+    <t>Not Automated</t>
+  </si>
+  <si>
+    <t>No automated coverage.</t>
+  </si>
+  <si>
     <t>TST_INVI_TC_12</t>
   </si>
   <si>
@@ -976,6 +1006,12 @@
   </si>
   <si>
     <t>**[CORRECTED 2026-09-14 — live pass]** DECISION [user, 2026-09-14]: run on &lt;ADMIN_USER&gt; and accept consuming one unread notification per run (93 unread ≈ 90 runs); click the OLDEST visible report-ready row. Read the count before and after in the same run — never an absolute number. The landing destination is still [ASSUMED] (not grounded, because a click cannot be undone). — Superseded note follows: Added 2026-09-01 from the other team's TC_GEN_003, whose steps click a notification and mark it read. All five of our notification cases (`TST_INVI_TC_7`–`TC_11`) are about **rendering** — badge, grouping, dates, wording — and none clicks a row. `TST_INVI_TC_7` already pairs the badge with its accessible name, so this closes the loop by proving the count actually changes. **Mutates state** (read status is not reversible) — keep out of side-effect-free suites.</t>
+  </si>
+  <si>
+    <t>Written - not wired</t>
+  </si>
+  <si>
+    <t>Handler exists in adminNotifications.test.js but no execution file runs it.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_34</t>
@@ -1437,7 +1473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:P42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1455,7 +1491,7 @@
     <col min="14" max="14" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1498,1813 +1534,2065 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="N3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="N9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O9" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="P9" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="J26" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="K26" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N26" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="s">
+      <c r="N27" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="P27" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="N27" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C32" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>209</v>
-      </c>
       <c r="E32" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>287</v>
+        <v>299</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Generic/AdminApp_Generic_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Generic/AdminApp_Generic_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="300">
   <si>
     <t>S.No.</t>
   </si>
@@ -53,6 +53,12 @@
   </si>
   <si>
     <t>Comments / Defect ID</t>
+  </si>
+  <si>
+    <t>Automation Status</t>
+  </si>
+  <si>
+    <t>Automation Evidence</t>
   </si>
   <si>
     <t>TST_ASHL_TC_1</t>
@@ -81,16 +87,22 @@
   </si>
   <si>
     <t xml:space="preserve">Exactly TWO options are offered, in this order: "English", then "Español".
-The active language ("English") is visually marked as the selected option, and the control's accessible name reads "Site language, English".</t>
-  </si>
-  <si>
-    <t>Grounded live 2026-08-27 from the pre-rendered DOM. Control qid "sp-ldd-cntr"; options "sp-ldd-btn-en" and "sp-ldd-btn-es". Selection is marked by the CSS class "selected-item" on the active option — that class, not styling, is the reliable check. The control appears in the HEADER when logged out and the FOOTER when logged in. DISTINCT FROM TST_LAND_TC_4, which covers the same control on the LANDING page — this case is the admin-app instance.</t>
+The active language ("English") carries the CSS class "active" and its accessible name ends ", selected"; the trigger's accessible name reads "Site language, English".</t>
+  </si>
+  <si>
+    <t>**[CORRECTED 2026-09-14 — live pass]** Logged-in qids were WRONG: the trigger is "cFooter-7" and the options are "cFooter-8-0" (English) and "cFooter-8-1" (Español) — "sp-ldd-*" does not exist when logged in (it is presumably the logged-out header control). The active option is marked by class "active", NOT "selected-item". — Superseded note follows: Grounded live 2026-08-27 from the pre-rendered DOM. Control qid "sp-ldd-cntr"; options "sp-ldd-btn-en" and "sp-ldd-btn-es". Selection is marked by the CSS class "selected-item" on the active option — that class, not styling, is the reliable check. The control appears in the HEADER when logged out and the FOOTER when logged in. DISTINCT FROM TST_LAND_TC_4, which covers the same control on the LANDING page — this case is the admin-app instance.</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Not Run</t>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Automated</t>
+  </si>
+  <si>
+    <t>Suite: adminGeneric | 2026-09-16: Pass across 2 runs</t>
   </si>
   <si>
     <t>TST_ASHL_TC_2</t>
@@ -106,15 +118,15 @@
 5. Switch back to "English".</t>
   </si>
   <si>
-    <t>Expected Spanish strings: to be added to appLangES.json once captured (see Remarks).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ASSUMED] After step 2 the admin interface re-renders in Spanish: the "My school accounts" heading, the footer links and the role toggle all show Spanish copy, and the language control now reads "Español" with "Español" marked selected.
-[ASSUMED] After step 4 the Spanish selection PERSISTS across the reload.
-After step 5 the interface returns to English.</t>
-  </si>
-  <si>
-    <t>⚠️ NOT GROUNDED — no admin-app Spanish copy has been verified. GENUINE GAP: appLangES.json exists but contains only "landing" and "login" sections — it has NO admin-app or footer entries, so the strings this case needs do not exist yet anywhere. When captured they should be added to appLangES.json under a new admin section, matching the existing appLangEN.json pattern. Whether the choice persists per-account server-side (as the class Filter and Search do, admin-shared.md §A4) or only for the session is specifically unknown. CHANGES ACCOUNT STATE: switches the language and must switch it back (step 5).</t>
+    <t>Verified Spanish copy (2026-09-14): School settings "Pautas del centro educativo"; footer "Términos de uso" · "Aviso de privacidad" · "Accesibilidad" · "Ayuda"; "Cambridge One para centros educativos"; Help "Ayuda"; trigger "Idioma del sitio, Español"; toggle "Interruptor Administrador/Profesor: Administrador actualmente activo, activar para ver el panel del Profesor".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After step 2 the interface re-renders IN PLACE (no reload) in Spanish: html lang becomes "es", Español carries class "active", and the strings listed in Test Data are shown.
+After step 4 the Spanish selection PERSISTS across the reload (stored in the browser's localStorage "comprodls.nemo.selected-locale").
+After step 5 the page RELOADS and returns to English (html lang "en").</t>
+  </si>
+  <si>
+    <t>**[CORRECTED 2026-09-14 — live pass]** GROUNDED LIVE 2026-09-14 on KNF-XRD-QVE (approved by the user). Persistence is PER-BROWSER, not per-account — a fresh browser context starts in English, so other suites are not affected. es→en reloads the page while en→es does not — the restore step must wait for a navigation. I18N DEFECTS found: footer "Our approach" is not translated; the bell's aria-label stays "Notifications (N unread notifications)". [CORRECTED 2026-09-15] The earlier claim that tab "Clases (10)" has a space before the count while the other tabs do not is WRONG — a live read found all five Spanish tabs share one format (label and count on separate lines: CLASES (10) · ALUMNOS (15) · PERSONAL (12) · BIBLIOTECA (974) · INFORMES (0)). Not a defect. "Pautas del centro educativo" (≈ guidelines) is a questionable translation — confirm with product. — Superseded note follows: ⚠️ NOT GROUNDED — no admin-app Spanish copy has been verified. GENUINE GAP: appLangES.json exists but contains only "landing" and "login" sections — it has NO admin-app or footer entries, so the strings this case needs do not exist yet anywhere. When captured they should be added to appLangES.json under a new admin section, matching the existing appLangEN.json pattern. Whether the choice persists per-account server-side (as the class Filter and Search do, admin-shared.md §A4) or only for the session is specifically unknown. CHANGES ACCOUNT STATE: switches the language and must switch it back (step 5).</t>
   </si>
   <si>
     <t>TST_MYPR_TC_1</t>
@@ -159,7 +171,7 @@
 Observed 2026-08-27 for &lt;ADMIN_USER&gt;: First name "Test", Last name "T1", Email "testt1@mailsac.com", Location "India".</t>
   </si>
   <si>
-    <t>GROUNDED LIVE 2026-08-27. Field qids "c-mp-inpt-1".."c-mp-inpt-4"; Update "c-mp-btn-3"; Cancel "c-mp-btn-4". Underlying Gigya names: profile.firstName / profile.lastName / profile.email / profile.country. ⚠️ The "Location" field has THREE identities — label "Location", name "profile.country", HTML id "gigya-textbox-zip" (zip, i.e. postcode). It behaves as a country ("India"). Select it by qid, and do not infer its meaning from the id. VALUES ARE ACCOUNT-SPECIFIC — use &lt;ADMIN_USER&gt; placeholders, never the literals above (admin-shared.md §A5).</t>
+    <t>**[CORRECTED 2026-09-14 — live pass]** Update is input[type=submit][value="Update"] (qid "c-mp-btn-3") — assert its value, its text is empty. Cancel on THIS tab is "c-mp-btn-2" — "c-mp-btn-4" is the Password tab's Cancel. Labels carry " *" (visually required) although no field has a required attribute. — Superseded note follows: GROUNDED LIVE 2026-08-27. Field qids "c-mp-inpt-1".."c-mp-inpt-4"; Update "c-mp-btn-3"; Cancel "c-mp-btn-4". Underlying Gigya names: profile.firstName / profile.lastName / profile.email / profile.country. ⚠️ The "Location" field has THREE identities — label "Location", name "profile.country", HTML id "gigya-textbox-zip" (zip, i.e. postcode). It behaves as a country ("India"). Select it by qid, and do not infer its meaning from the id. VALUES ARE ACCOUNT-SPECIFIC — use &lt;ADMIN_USER&gt; placeholders, never the literals above (admin-shared.md §A5).</t>
   </si>
   <si>
     <t>TST_MYPR_TC_3</t>
@@ -181,7 +193,7 @@
 All three inputs mask their content (type=password).</t>
   </si>
   <si>
-    <t>GROUNDED LIVE 2026-08-27. Field qids "c-mp-inpt-5".."c-mp-inpt-7"; Update "c-mp-btn-5". Gigya names: password / newPassword / passwordRetype. ⚠️ The URL does NOT change between tabs — both are /dashboard/my-profile. The Password tab therefore CANNOT be deep-linked, and the active tab cannot be asserted from the URL. Combined with the missing aria-selected (TST_MYPR_TC_8) there is currently NO reliable attribute identifying the active tab — automation must assert on the visible fields instead.</t>
+    <t>**[CORRECTED 2026-09-14 — live pass]** The active tab IS identifiable: the parent li gets class "selected" (li.password-tab … selected) — this corrects "there is currently NO reliable attribute identifying the active tab". Cancel on this tab is "c-mp-btn-4". The tabs swap DOM (Personal-info inputs are removed) and the swap takes more than 1 s. — Superseded note follows: GROUNDED LIVE 2026-08-27. Field qids "c-mp-inpt-5".."c-mp-inpt-7"; Update "c-mp-btn-5". Gigya names: password / newPassword / passwordRetype. ⚠️ The URL does NOT change between tabs — both are /dashboard/my-profile. The Password tab therefore CANNOT be deep-linked, and the active tab cannot be asserted from the URL. Combined with the missing aria-selected (TST_MYPR_TC_8) there is currently NO reliable attribute identifying the active tab — automation must assert on the visible fields instead.</t>
   </si>
   <si>
     <t>TST_MYPR_TC_4</t>
@@ -234,7 +246,16 @@
 [ASSUMED] After step 4 the server rejects the value with a validation message, or accepts and truncates it. Capture which, and the exact message.</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED PARTIALLY 2026-08-27: the ABSENCE of a limit is verified — ALL SEVEN fields across both tabs have maxlength=null and none is marked required. What the SERVER does is [ASSUMED]. This is a deliberate departure from the rest of the admin app, where limits are declared and enforced client-side (class name 50, grading scale title 20 — admin-shared.md §A3). Because nothing is declared here, boundary cases CANNOT be derived from the markup and must be found by submitting. ⚠️ DO NOT RUN ON &lt;ADMIN_USER&gt; — that account is the login for the whole admin suite. Blocked until a disposable account exists.</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED PARTIALLY 2026-08-27: the ABSENCE of a limit is verified — ALL SEVEN fields across both tabs have maxlength=null and none is marked required. What the SERVER does is [ASSUMED]. This is a deliberate departure from the rest of the admin app, where limits are declared and enforced client-side (class name 50, grading scale title 20 — admin-shared.md §A3). Because nothing is declared here, boundary cases CANNOT be derived from the markup and must be found by submitting. ⚠️ DO NOT RUN ON &lt;ADMIN_USER&gt; — that account is the login for the whole admin suite. Blocked until a disposable account exists.</t>
+  </si>
+  <si>
+    <t>Not Run</t>
+  </si>
+  <si>
+    <t>Excluded - Phase 1</t>
+  </si>
+  <si>
+    <t>Out of Phase 1 automation scope.</t>
   </si>
   <si>
     <t>TST_MYPR_TC_6</t>
@@ -261,7 +282,7 @@
     <t>[ASSUMED] The password is NOT changed and a mismatch validation message is shown against the confirmation field.</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. ⚠️ ERROR COPY NOT CAPTURED — nothing was submitted, by agreement, because &lt;ADMIN_USER&gt; is the admin suite's login account. The message text must be captured on a disposable account. For reference the equivalent page in the other app exposes a dedicated error element ("confirmPasswordError_text" in the SETT selector set), so a field-level message is expected here too — but that is the OTHER app and must not be assumed identical. DESTRUCTIVE IF IT SUCCEEDS: a mistyped variant of this case would change a real password.</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. ⚠️ ERROR COPY NOT CAPTURED — nothing was submitted, by agreement, because &lt;ADMIN_USER&gt; is the admin suite's login account. The message text must be captured on a disposable account. For reference the equivalent page in the other app exposes a dedicated error element ("confirmPasswordError_text" in the SETT selector set), so a field-level message is expected here too — but that is the OTHER app and must not be assumed identical. DESTRUCTIVE IF IT SUCCEEDS: a mistyped variant of this case would change a real password.</t>
   </si>
   <si>
     <t>TST_MYPR_TC_7</t>
@@ -281,7 +302,7 @@
     <t>[ASSUMED] The password is NOT changed and an error identifies the old password as incorrect.</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. ⚠️ ERROR COPY NOT CAPTURED — see TST_MYPR_TC_6. The SETT selector set has a matching "currentPasswordError_text" element in the other app. Worth checking whether repeated failures lock the account, which would affect suite design.</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. ⚠️ ERROR COPY NOT CAPTURED — see TST_MYPR_TC_6. The SETT selector set has a matching "currentPasswordError_text" element in the other app. Worth checking whether repeated failures lock the account, which would affect suite design.</t>
   </si>
   <si>
     <t>TST_MYPR_TC_8</t>
@@ -299,7 +320,7 @@
 ACTUAL (2026-08-27): this FAILS. Both are plain &lt;a&gt; elements with NO role="tab" and NO aria-selected. Nothing in the markup or the URL identifies the active tab.</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. Raised as a case because it is both an accessibility gap and an automation blocker: with no aria-selected AND no URL change between tabs (TST_MYPR_TC_3), there is no attribute to assert the active tab on — automation must fall back to checking which fields are visible. Confirm with the product team whether this should be raised as a defect. Tab qids "c-mp-tab-1" (Personal info) and "c-mp-tab-2" (Password).</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. Raised as a case because it is both an accessibility gap and an automation blocker: with no aria-selected AND no URL change between tabs (TST_MYPR_TC_3), there is no attribute to assert the active tab on — automation must fall back to checking which fields are visible. Confirm with the product team whether this should be raised as a defect. Tab qids "c-mp-tab-1" (Personal info) and "c-mp-tab-2" (Password).</t>
   </si>
   <si>
     <t>TST_INVI_TC_7</t>
@@ -344,7 +365,7 @@
 Observed 2026-08-27: heading "Notifications (92)" matching the badge; both time groups present.</t>
   </si>
   <si>
-    <t>GROUNDED LIVE 2026-08-27 — the panel was opened manually and read in full, resolving the earlier [ASSUMED] version of this case. GENUINE GAP: TST_INVI_TC_1..6 cover the INVITATION-ACCEPT flow reached through this bell (invitationNotify → selectCheckbox → acceptBtn → goToDashboard); they do NOT cover this panel. Selectors: panel ".notification-dropdown"; heading ".notification-heading" h2 with span.readCount; time groups "p.time-related-title"; rows "button.tippy-dropdown-item"; footer link qid "ntf-4". ⚠️ The close "×" carries qid "ntf-2" on TWO visible elements (".close" and ".close-dummy") — address it by class, not qid. Same trap shape as cFooter-9. NOT pre-rendered — built lazily by tippy.js, so it must actually be opened (admin-shared.md §A6 does not apply here). The EMPTY state was not seen — this account has 92 notifications. [ASSUMED] and still open.</t>
+    <t>**[CORRECTED 2026-09-14 — live pass]** ".notification-dropdown" is the 56 px wrapper AROUND THE BELL, not the panel — do not use it as the panel selector. Count was 93 on 2026-09-14 (never assert an absolute count). Opening the panel does NOT change the unread count (93 before, 93 after). — Superseded note follows: GROUNDED LIVE 2026-08-27 — the panel was opened manually and read in full, resolving the earlier [ASSUMED] version of this case. GENUINE GAP: TST_INVI_TC_1..6 cover the INVITATION-ACCEPT flow reached through this bell (invitationNotify → selectCheckbox → acceptBtn → goToDashboard); they do NOT cover this panel. Selectors: panel ".notification-dropdown"; heading ".notification-heading" h2 with span.readCount; time groups "p.time-related-title"; rows "button.tippy-dropdown-item"; footer link qid "ntf-4". ⚠️ The close "×" carries qid "ntf-2" on TWO visible elements (".close" and ".close-dummy") — address it by class, not qid. Same trap shape as cFooter-9. NOT pre-rendered — built lazily by tippy.js, so it must actually be opened (admin-shared.md §A6 does not apply here). The EMPTY state was not seen — this account has 92 notifications. [ASSUMED] and still open.</t>
   </si>
   <si>
     <t>TST_INVI_TC_9</t>
@@ -399,19 +420,18 @@
     <t>Low</t>
   </si>
   <si>
-    <t>Logged in as school-admin &lt;ADMIN_USER&gt; on Thor; "My school accounts" (/admin/admin/dashboard) displayed. The account has both "Class summary" and "Aggregated data" report-ready notifications.</t>
+    <t>Logged in as school-admin &lt;ADMIN_USER&gt; on Thor; "My school accounts" (/admin/admin/dashboard) displayed. The account has report-ready notifications of more than one report type.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Click the notifications bell.
-2. Read the body line of a "Your Class summary report is ready" row.
-3. Read the body line of a "Your Aggregated data report is ready" row.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Both notifications refer to the same destination in the same words.
-ACTUAL (2026-08-27): they do NOT. Class summary reads "View your report, available to download in the Reports tab", while Aggregated data reads "View your report, available to download on the Reports page" — "Reports tab" vs "Reports page".</t>
-  </si>
-  <si>
-    <t>Grounded live 2026-08-27, both strings captured verbatim from the same open panel. A low-severity copy inconsistency, raised as a case so it is not rediscovered during automation and so any verbatim-copy assertion is written against the correct string per notification type. Confirm with the product team whether this is intended before raising a ticket. Full failure copy also captured: "Sorry, something went wrong. The &lt;TYPE&gt; report you requested failed to generate. Details available in the Reports tab".</t>
+2. For each report-ready row, read its title and its body line.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every report-ready notification refers to the Reports destination in the same words.
+ACTUAL (2026-09-14): they do NOT. "Your Assignments summary report is ready" reads "…available to download on the Reports page", while "Your Class summary report is ready", "Your Aggregated data report is ready" and "Your Class daily data report is ready" read "…available to download in the Reports tab".</t>
+  </si>
+  <si>
+    <t>**[CORRECTED 2026-09-14 — live pass]** The inconsistency is real but the recorded PAIRING was stale: on 2026-09-14 "on the Reports page" belongs to Assignments summary and Aggregated data reads "in the Reports tab". Assert per notification TYPE, and read the rows present at run time — the five visible rows change as reports are generated. — Superseded note follows: Grounded live 2026-08-27, both strings captured verbatim from the same open panel. A low-severity copy inconsistency, raised as a case so it is not rediscovered during automation and so any verbatim-copy assertion is written against the correct string per notification type. Confirm with the product team whether this is intended before raising a ticket. Full failure copy also captured: "Sorry, something went wrong. The &lt;TYPE&gt; report you requested failed to generate. Details available in the Reports tab".</t>
   </si>
   <si>
     <t>TST_ASHL_TC_3</t>
@@ -479,7 +499,7 @@
 "CLASSES" is the active tab by default, the page heading shows the school name, and the browser tab reads "Classes | Cambridge One".</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. Tab qids "aDetail-1" (Classes), "aDetail-2" (Students), "aDetail-4" (Staff), "aDetail-5" (Library), "aDetail-6" (Reports). ⚠️ "aDetail-3" IS SKIPPED — the sequence is 1,2,4,5,6. Do not iterate 1..5 assuming contiguity. ⚠️ THE ACTIVE MARKER IS ON THE PARENT &lt;li&gt;, not the anchor: "li.nav-item.active &gt; a". The anchor className is identical on every tab whether active or not, so asserting on the link class is a guaranteed false green. Labels render UPPER CASE — confirm whether that is CSS text-transform or the actual text before asserting case-sensitively.</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. Tab qids "aDetail-1" (Classes), "aDetail-2" (Students), "aDetail-4" (Staff), "aDetail-5" (Library), "aDetail-6" (Reports). ⚠️ "aDetail-3" IS SKIPPED — the sequence is 1,2,4,5,6. Do not iterate 1..5 assuming contiguity. ⚠️ THE ACTIVE MARKER IS ON THE PARENT &lt;li&gt;, not the anchor: "li.nav-item.active &gt; a". The anchor className is identical on every tab whether active or not, so asserting on the link class is a guaranteed false green. Labels render UPPER CASE — confirm whether that is CSS text-transform or the actual text before asserting case-sensitively.</t>
   </si>
   <si>
     <t>TST_ASHL_TC_6</t>
@@ -508,7 +528,7 @@
 The school heading stays unchanged throughout.</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27 — all five walked and every URL and title confirmed. ⚠️ NOTE the STUDENTS tab routes to "/learner", NOT "/student". A URL assertion built from the tab label will fail on this one. Tabs carry REAL hrefs (unlike the footer, whose logged-in hrefs collapse to javascript:void(0) — TST_FOOT_TC_10 remarks), so tab navigation is genuinely href-driven. TIMING measured this session: Reports took ~4.3 s to become active, Classes ~1.2 s. Poll for "li.nav-item.active &gt; a" carrying the expected qid rather than using a fixed pause (admin-shared.md §B8).</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27 — all five walked and every URL and title confirmed. ⚠️ NOTE the STUDENTS tab routes to "/learner", NOT "/student". A URL assertion built from the tab label will fail on this one. Tabs carry REAL hrefs (unlike the footer, whose logged-in hrefs collapse to javascript:void(0) — TST_FOOT_TC_10 remarks), so tab navigation is genuinely href-driven. TIMING measured this session: Reports took ~4.3 s to become active, Classes ~1.2 s. Poll for "li.nav-item.active &gt; a" carrying the expected qid rather than using a fixed pause (admin-shared.md §B8).</t>
   </si>
   <si>
     <t>TST_ASHL_TC_7</t>
@@ -528,7 +548,7 @@
 ACTUAL (2026-08-27): this FAILS. No tab link carries aria-current or aria-selected; the only indicator is the "active" CSS class on the parent &lt;li&gt;, which is presentational.</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. This is the SECOND instance of the same gap in this batch — the My Profile tabs have it too (TST_MYPR_TC_8). Worth raising as one combined accessibility ticket rather than two. The school tabs are at least recoverable for automation via "li.nav-item.active"; the profile tabs have no indicator at all, which makes them the more severe of the two.</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. This is the SECOND instance of the same gap in this batch — the My Profile tabs have it too (TST_MYPR_TC_8). Worth raising as one combined accessibility ticket rather than two. The school tabs are at least recoverable for automation via "li.nav-item.active"; the profile tabs have no indicator at all, which makes them the more severe of the two.</t>
   </si>
   <si>
     <t>TST_FOOT_TC_10</t>
@@ -596,7 +616,7 @@
 Two controls are offered: "Continue" and "Cancel".</t>
   </si>
   <si>
-    <t>COPY GROUNDED LIVE 2026-08-27 — captured VERBATIM from the pre-rendered DOM (admin-shared.md §A6) WITHOUT triggering the action, which is the only safe way to verify it on a shared school. Dialog buttons: Continue "adEdit-3", Cancel "adEdit-4". The expected copy is therefore VERIFIED even though the dialog was never opened; only the act of opening it is [ASSUMED].</t>
+    <t>**[CORRECTED 2026-09-14 — live pass]** Opening the warning is now VERIFIED live (KNF-XRD-QVE, 2026-09-14) — the copy matched verbatim. Scope every dialog selector with "#changeSchoolKey" (the Classes tab holds 5 .modal-content). The warning icon is "div.warning-heading &gt; i.fa.fa-exclamation-triangle". Continue and Cancel are anchors. — Superseded note follows: COPY GROUNDED LIVE 2026-08-27 — captured VERBATIM from the pre-rendered DOM (admin-shared.md §A6) WITHOUT triggering the action, which is the only safe way to verify it on a shared school. Dialog buttons: Continue "adEdit-3", Cancel "adEdit-4". The expected copy is therefore VERIFIED even though the dialog was never opened; only the act of opening it is [ASSUMED].</t>
   </si>
   <si>
     <t>TST_SKEY_TC_3</t>
@@ -632,10 +652,16 @@
     <t>BLOCKED at design time 2026-08-27 — IRREVERSIBLE ACTION ON A SHARED SCHOOL. The product itself states "Changing the school key cannot be undone". Unblock with a DEDICATED, DISPOSABLE school that no suite depends on.</t>
   </si>
   <si>
+    <t>BLOCKED - see Comments for the blocker and its unblock route</t>
+  </si>
+  <si>
     <t>TST_SKEY_TC_4</t>
   </si>
   <si>
     <t>Verify the school key is unchanged when the warning dialog is cancelled</t>
+  </si>
+  <si>
+    <t>Logged in as school-admin &lt;ADMIN_USER&gt; on Thor; school KNF-XRD-QVE ("3 July Test School 2") opened from "My school accounts" — NEVER FCN-CHZ-PDA; Classes tab displayed.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Note the current school key.
@@ -644,10 +670,13 @@
 4. Re-read the school key.</t>
   </si>
   <si>
-    <t>[ASSUMED] The dialog closes and the school key is UNCHANGED.</t>
-  </si>
-  <si>
-    <t>⚠️ EXPECTED RESULT NOT VERIFIED — the dialog was never opened, by design, on the shared school. This is the SAFE half of the flow and is the one case here that could reasonably be run on a shared school, PROVIDED Cancel is clicked and never Continue. Even so, treat it carefully: a misclick is irreversible. Cancel qid "adEdit-4". Also confirm whether dismissing via Esc or a backdrop click behaves the same as Cancel.</t>
+    <t>School key: KNF-XRD-QVE</t>
+  </si>
+  <si>
+    <t>The dialog closes — the modal is display:none, no .modal-backdrop remains and body.modal-open is removed — and the school key displayed on the Classes tab is UNCHANGED.</t>
+  </si>
+  <si>
+    <t>**[CORRECTED 2026-09-14 — live pass]** DECISION [user, 2026-09-14]: run on KNF-XRD-QVE, never FCN-CHZ-PDA. KEY UNCHANGED is VERIFIED live (before / while open / after all "KNF-XRD-QVE"). "Closed" must be checked with all three signals — the "show" class alone reports closed while the backdrop still covers the page. [ASSUMED] that a REAL click on Cancel closes it: during grounding a SYNTHETIC click on Cancel (a[data-dismiss=modal]) did not, Escape did (fade within 1.5 s), and the grounding browser's real input was not working that day. — Superseded note follows: ⚠️ EXPECTED RESULT NOT VERIFIED — the dialog was never opened, by design, on the shared school. This is the SAFE half of the flow and is the one case here that could reasonably be run on a shared school, PROVIDED Cancel is clicked and never Continue. Even so, treat it carefully: a misclick is irreversible. Cancel qid "adEdit-4". Also confirm whether dismissing via Esc or a backdrop click behaves the same as Cancel.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_32</t>
@@ -700,7 +729,7 @@
 Observed 2026-08-27 for &lt;ADMIN_USER&gt;: 7 schools, numbered 01–07.</t>
   </si>
   <si>
-    <t xml:space="preserve">[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. Card qid "aDashboard-N" (a.inst-link); chevron is a SEPARATE "aDashboard1-N". Both are POSITIONAL. The school key is carried in the card's aria-label, which is what makes key-based selection possible (schoolAdminDashboard.schoolLinkByKey uses a.inst-link[aria-label*="{{key}}"]).
+    <t xml:space="preserve">**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. Card qid "aDashboard-N" (a.inst-link); chevron is a SEPARATE "aDashboard1-N". Both are POSITIONAL. The school key is carried in the card's aria-label, which is what makes key-based selection possible (schoolAdminDashboard.schoolLinkByKey uses a.inst-link[aria-label*="{{key}}"]).
 ⚠️ NEVER assert the literal count 7 — this is a shared account and the list changes (admin-shared.md §A5). Assert the card STRUCTURE and that the expected key is present.
 Extends the existing SADB module (TST_SADB_TC_1 opens a school by key) — that case already covers opening; this one covers the LISTING, which nothing did.
 ⚠️ EXTENDS admin-shared.md §0, which documents 4 schools. This account sees 7 — KNF-XRD-QVE, HQC-ZWM-ZVF and GYB-JMU-KYA were undocumented.</t>
@@ -718,14 +747,13 @@
 4. Compare the Classes listings of the two.</t>
   </si>
   <si>
-    <t>Schools: &lt;SCHOOL_KEY_A&gt; and &lt;SCHOOL_KEY_B&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each school opens under its own org slug, /admin/admin/org_&lt;slug&gt;/class, with its own name as the page heading and its own class list. No content from the previously opened school persists.
-Observed 2026-08-27: "3 July Test School 1" (FCN-CHZ-PDA) opened as org_perf_testschool_1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GROUNDED PARTIALLY 2026-08-27 — one school was opened and its slug confirmed; the SWITCH between two schools was not exercised, so step 4 is [ASSUMED].
+    <t>Schools: FCN-CHZ-PDA ("3 July Test School 1") and KNF-XRD-QVE ("3 July Test School 2")</t>
+  </si>
+  <si>
+    <t>Each school opens under its own org slug with its own heading and its own school key: FCN-CHZ-PDA → /admin/admin/org_perf_testschool_1/class, "3 July Test School 1"; KNF-XRD-QVE → /admin/admin/org_perf_testschool_2/class, "3 July Test School 2". No content from the previously opened school persists — e.g. the FCN-only fixture class "Fixture_GradeSettings_DO_NOT_DELETE" is absent from KNF-XRD-QVE.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**[CORRECTED 2026-09-14 — live pass]** Step 4 VERIFIED live 2026-09-14 by switching FCN-CHZ-PDA → KNF-XRD-QVE. The fixture-class absence is a falsifiable no-carry-over check; never assert class COUNTS (both schools are shared and mutable). — Superseded note follows: GROUNDED PARTIALLY 2026-08-27 — one school was opened and its slug confirmed; the SWITCH between two schools was not exercised, so step 4 is [ASSUMED].
 ⚠️ The org slug is NOT derivable from the school name or key — "3 July Test School 1" (FCN-CHZ-PDA) maps to org_perf_testschool_1. Capture each slug; never construct it.
 The school context MUST be set by clicking the card — deep-linking /admin/admin/org_&lt;slug&gt;/class returns /dashboard/error even when authenticated (admin-shared.md §A1).
 Worth checking whether the per-account server-side class Filter and Search (§A4) are scoped per school or leak across organisations — that is unknown and would be a real defect if they leak.</t>
@@ -751,7 +779,7 @@
     <t>Both cards show the SAME display name but DIFFERENT school keys, and the card selected by key opens that specific school.</t>
   </si>
   <si>
-    <t xml:space="preserve">[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27 — cards 01 and 02 both read "3 July Test School 1" with keys FCN-CHZ-PDA and ZPB-TWP-AEQ, and identical addresses too.
+    <t xml:space="preserve">**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27 — cards 01 and 02 both read "3 July Test School 1" with keys FCN-CHZ-PDA and ZPB-TWP-AEQ, and identical addresses too.
 ⚠️ THIS IS THE CASE THAT JUSTIFIES admin-shared.md §0's standing rule: ALWAYS select a school by KEY, never by name or card position. Selecting by name is ambiguous here, and card qids (aDashboard-N) are positional so they re-issue when the list changes.
 Confirming WHICH school loaded (step 3) needs a distinguishing feature — the org slug in the URL is the reliable one, since the heading shows the shared name.</t>
   </si>
@@ -791,7 +819,7 @@
     <t>Verify each wizard step blocks progress until its required input is supplied</t>
   </si>
   <si>
-    <t>The "Set up a school account" wizard is open at step 2 (School type).</t>
+    <t>Logged in as school-admin &lt;ADMIN_USER&gt; on Thor; the "Set up a school account" wizard (/dashboard/teacher/setupschool) open at School type.</t>
   </si>
   <si>
     <t xml:space="preserve">1. On School type, without selecting an option, attempt to continue.
@@ -799,10 +827,16 @@
 3. Repeat the same check for Number of teachers, School name, School location, School address and School contact details.</t>
   </si>
   <si>
-    <t>[ASSUMED] On each step the Next control is unavailable until that step's required input is supplied, and becomes available once it is. No step can be skipped.</t>
-  </si>
-  <si>
-    <t>⚠️ EXPECTED RESULT NOT VERIFIED — the wizard was not walked in this session. INFERRED from the existing automation, whose case titles state the enabling direction only, e.g. TST_SCTY_TC_3 "Select first radio option (Primary school) to ENABLE Next button" and TST_SNAM_TC_3 "Fill school name field to ENABLE Next button". The DISABLED half is nowhere asserted, which is the gap this case fills. Confirm whether Next is natively disabled or only CSS-disabled — admin-shared.md §B4 records CSS-only disabling elsewhere in this app, which would make a naive enabled-state check a false green. SIDE-EFFECT FREE: stops short of submission.</t>
+    <t xml:space="preserve">On every step the Next button is NATIVELY disabled until that step is valid, then enabled:
+School type / Number of teachers — until an option is selected.
+School name — until non-whitespace text is entered.
+Location — arrives pre-filled from the account; clearing it, whitespace, or a partial value ("Ind") disables Next.
+Address — Street address AND City / town are both required; Region and Postal code are optional.
+Telephone — telephone code AND a numeric telephone number are required; the website URL is optional but a malformed one ("example") disables Next.
+No step shows an inline error; the disabled Next is the only signal. The summary is reached; "Send Request" is NOT clicked.</t>
+  </si>
+  <si>
+    <t>**[CORRECTED 2026-09-14 — live pass]** VERIFIED LIVE 2026-09-14 — walked to the summary, never submitted. Next is NATIVELY disabled (disabled attribute + .disabled + pointer-events none), so an isEnabled assertion is valid. The wizard advances IN-PAGE (URL never changes) and the Next qid differs per step. ⚠️ The existing wizard modules' generic "button.btn-purple" also matches "Send Request" (t-ss-as-btn-1) — stop by qid. The summary omits school type and number of teachers. — Superseded note follows: ⚠️ EXPECTED RESULT NOT VERIFIED — the wizard was not walked in this session. INFERRED from the existing automation, whose case titles state the enabling direction only, e.g. TST_SCTY_TC_3 "Select first radio option (Primary school) to ENABLE Next button" and TST_SNAM_TC_3 "Fill school name field to ENABLE Next button". The DISABLED half is nowhere asserted, which is the gap this case fills. Confirm whether Next is natively disabled or only CSS-disabled — admin-shared.md §B4 records CSS-only disabling elsewhere in this app, which would make a naive enabled-state check a false green. SIDE-EFFECT FREE: stops short of submission.</t>
   </si>
   <si>
     <t>TST_ASHL_TC_8</t>
@@ -821,7 +855,7 @@
     <t>On every tab, no dialog, warning or error is visible on load. The screen shows only its own content.</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27 — verified that every dialog present in the DOM was hidden on load (Classes 5, Students 4, Staff 1; all offsetParent === null). ⚠️ THIS IS THE HEADLINE AUTOMATION TRAP FOR THIS SCENARIO. Admin dialogs are PRE-RENDERED, so they exist in the DOM before anything triggers them. Any check of the form "getElementCount(dialog) &gt; 0" therefore passes ALWAYS and proves nothing — admin-shared.md §B2 records this silently breaking reset_filters for weeks. Assert VISIBILITY, never presence. Note also that opacity:0 still counts as visible to Playwright; only display:none is hidden.</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27 — verified that every dialog present in the DOM was hidden on load (Classes 5, Students 4, Staff 1; all offsetParent === null). ⚠️ THIS IS THE HEADLINE AUTOMATION TRAP FOR THIS SCENARIO. Admin dialogs are PRE-RENDERED, so they exist in the DOM before anything triggers them. Any check of the form "getElementCount(dialog) &gt; 0" therefore passes ALWAYS and proves nothing — admin-shared.md §B2 records this silently breaking reset_filters for weeks. Assert VISIBILITY, never presence. Note also that opacity:0 still counts as visible to Playwright; only display:none is hidden.</t>
   </si>
   <si>
     <t>TST_ASHL_TC_9</t>
@@ -841,7 +875,7 @@
 Both offer a "Close" control.</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. COPY GROUNDED LIVE 2026-08-27 — both captured VERBATIM from the pre-rendered DOM (§A6) without reaching the capped state, which would otherwise require 51+ rows. Note the VERB differs with the domain — "delete" for classes, "remove" for students — so a single shared assertion string is wrong. The LIMIT (50) and the sentence shape are the consistent parts. Reaching these states for real is Blocked on the shared school (admin-shared.md §A5: it holds 26 students, so the 50-student cap cannot be hit).</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. COPY GROUNDED LIVE 2026-08-27 — both captured VERBATIM from the pre-rendered DOM (§A6) without reaching the capped state, which would otherwise require 51+ rows. Note the VERB differs with the domain — "delete" for classes, "remove" for students — so a single shared assertion string is wrong. The LIMIT (50) and the sentence shape are the consistent parts. Reaching these states for real is Blocked on the shared school (admin-shared.md §A5: it holds 26 students, so the 50-student cap cannot be hit).</t>
   </si>
   <si>
     <t>TST_ASHL_TC_10</t>
@@ -862,7 +896,7 @@
 Change school key — "CAREFUL!" / "Changing the school key cannot be undone" / "Cancel"</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. ALL THREE CAPTURED VERBATIM 2026-08-27 from the pre-rendered DOM, without triggering any of them — which is the only safe way, since all three are destructive on a shared school. ⚠️ The change-school-key dialog is present on EVERY admin tab (Classes, Students, Staff all carry it) because School settings lives in the shared page chrome — scope any modal selector with :has(...) to the specific dialog, or it will match this one everywhere. Async follow-ups are also pre-rendered and worth checking in the same pass: "This will take a few minutes" (classes) and "Removing students may take some time" (students).</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. ALL THREE CAPTURED VERBATIM 2026-08-27 from the pre-rendered DOM, without triggering any of them — which is the only safe way, since all three are destructive on a shared school. ⚠️ The change-school-key dialog is present on EVERY admin tab (Classes, Students, Staff all carry it) because School settings lives in the shared page chrome — scope any modal selector with :has(...) to the specific dialog, or it will match this one everywhere. Async follow-ups are also pre-rendered and worth checking in the same pass: "This will take a few minutes" (classes) and "Removing students may take some time" (students).</t>
   </si>
   <si>
     <t>TST_SADB_TC_5</t>
@@ -881,11 +915,11 @@
 5. Confirm the administrator view is restored.</t>
   </si>
   <si>
-    <t xml:space="preserve">After step 2 the browser navigates to /dashboard/teacher/dashboard, the browser tab reads "Teacher dashboard | Cambridge One", the page greets the user ("Hi &lt;FIRST_NAME&gt;!") and the toggle now reports "Teacher currently active".
-After step 4 the browser returns to /admin/admin/dashboard, titled "My school accounts | Cambridge One", and the toggle reports "Administrator currently active".</t>
-  </si>
-  <si>
-    <t>GROUNDED LIVE 2026-08-27 — the full round trip was performed and the account was left in Administrator view. ⚠️ THE SWITCH ELEMENT IS NAMED DIFFERENTLY IN EACH VIEW: ".can-toggle__switch" (double underscore) in the admin view, ".can-toggle-switch" (single hyphen) in the teacher view. A selector written for one view SILENTLY FAILS to find it in the other, which breaks exactly the round trip this case exercises. Use "#teacher-admin-toggle" (stable in both) and read the input's checked state — false = Administrator, true = Teacher. The focusable control is the inner [tabindex="0"] div; the input itself is aria-hidden. The toggle also appears on inner admin tabs, not just the dashboard. Existing selector schoolAdminDashboard.teacherAdminToggle already targets the input; this extends SADB. SIDE-EFFECT FREE — a view switch only.</t>
+    <t xml:space="preserve">After step 2 the browser navigates to /dashboard/teacher/dashboard, the page greets the user ("Hi &lt;FIRST_NAME&gt;!"), #teacher-admin-toggle is checked and the switch's accessible name reports "Teacher currently active".
+After step 4 the browser returns to the ADMIN PAGE THE TOGGLE WAS LEFT FROM — /admin/admin/dashboard when started there — #teacher-admin-toggle is unchecked and the accessible name reports "Administrator currently active".</t>
+  </si>
+  <si>
+    <t>**[CORRECTED 2026-09-14 — live pass]** Toggling back returns to the admin page the round trip STARTED on (verified from /class on 2026-09-14), so start this case on the dashboard. Do NOT assert the document title — it varies with the load path ("Administrator | Cambridge One" vs "My school accounts | Cambridge One"). — Superseded note follows: GROUNDED LIVE 2026-08-27 — the full round trip was performed and the account was left in Administrator view. ⚠️ THE SWITCH ELEMENT IS NAMED DIFFERENTLY IN EACH VIEW: ".can-toggle__switch" (double underscore) in the admin view, ".can-toggle-switch" (single hyphen) in the teacher view. A selector written for one view SILENTLY FAILS to find it in the other, which breaks exactly the round trip this case exercises. Use "#teacher-admin-toggle" (stable in both) and read the input's checked state — false = Administrator, true = Teacher. The focusable control is the inner [tabindex="0"] div; the input itself is aria-hidden. The toggle also appears on inner admin tabs, not just the dashboard. Existing selector schoolAdminDashboard.teacherAdminToggle already targets the input; this extends SADB. SIDE-EFFECT FREE — a view switch only.</t>
   </si>
   <si>
     <t>TST_SADB_TC_6</t>
@@ -907,7 +941,7 @@
 Observed 2026-08-27: administrator view 7 schools; teacher view 8 school groups, including "ABERYSTWYTH COLLEGE : THOR" and "LTI INTEGRATIONS TEST2", neither of which appears in the administrator list.</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. This matters because it is easy to assume the two views show the same estate — they do not, and a test asserting equal school counts across the toggle will fail. ⚠️ The teacher view groups by school DISPLAY NAME, so the two distinct schools both called "3 July Test School 1" (FCN-CHZ-PDA and ZPB-TWP-AEQ) collapse into a SINGLE group there. The admin view keeps them separate via their keys. Do not match schools across the two views by name. ⚠️ NEVER assert the literal counts 7 and 8 — shared account (§A5). Assert the RELATIONSHIP: the teacher list contains at least one school the admin list does not. ⚠️ Every "Create class" button in the teacher view shares qid "tDashboard-ncls-btn-1" — 7 elements, one per school group. See TST_SADB_TC_7.</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. This matters because it is easy to assume the two views show the same estate — they do not, and a test asserting equal school counts across the toggle will fail. ⚠️ The teacher view groups by school DISPLAY NAME, so the two distinct schools both called "3 July Test School 1" (FCN-CHZ-PDA and ZPB-TWP-AEQ) collapse into a SINGLE group there. The admin view keeps them separate via their keys. Do not match schools across the two views by name. ⚠️ NEVER assert the literal counts 7 and 8 — shared account (§A5). Assert the RELATIONSHIP: the teacher list contains at least one school the admin list does not. ⚠️ Every "Create class" button in the teacher view shares qid "tDashboard-ncls-btn-1" — 7 elements, one per school group. See TST_SADB_TC_7.</t>
   </si>
   <si>
     <t>TST_SADB_TC_7</t>
@@ -930,41 +964,54 @@
 6. Search for the class by name.</t>
   </si>
   <si>
-    <t>School: &lt;SCHOOL_KEY&gt; · Class name: "AutoClass_TeacherView_&lt;RUN_ID&gt;"</t>
+    <t>School: KNF-XRD-QVE ("3 July Test School 2") · Class name: "AutoClass_TeacherView_&lt;RUN_ID&gt;"</t>
   </si>
   <si>
     <t>[ASSUMED] The class is created under the chosen school and, after step 6, is listed in that school's Admin Classes tab under the same name.</t>
   </si>
   <si>
-    <t xml:space="preserve">⚠️ CREATES REAL DATA — a real class on a real school. This decides suite placement absolutely: it must NOT sit in a side-effect-free suite. Use the sweepable "AutoClass_" prefix (admin-shared.md §A7) so leftovers are recognisable, and note that class DELETE is SOFT, so every run leaves a permanent soft-deleted row (§A5).
+    <t xml:space="preserve">**[CORRECTED 2026-09-14 — live pass]** DECISION [user, 2026-09-14]: run on KNF-XRD-QVE in its OWN data-owning suite — never in the read-only Generic suite. Sweep AutoClass_TeacherView_ leftovers on KNF before creating; delete the created class by its URL afterwards. The school's name is unique in the teacher view. — Superseded note follows: ⚠️ CREATES REAL DATA — a real class on a real school. This decides suite placement absolutely: it must NOT sit in a side-effect-free suite. Use the sweepable "AutoClass_" prefix (admin-shared.md §A7) so leftovers are recognisable, and note that class DELETE is SOFT, so every run leaves a permanent soft-deleted row (§A5).
 ⚠️ CHOOSING THE RIGHT "Create class" IS THE HARD PART. All 7 buttons in the teacher view share qid "tDashboard-ncls-btn-1", one per school group, and the qid cannot distinguish them. The button must be located THROUGH its school-group heading, or the class lands on the wrong school. A class literally named "admin as a teacher class" already exists under MQA Sierra School, suggesting this has been done manually before.
 ⚠️ CLASS CREATION IS ASYNCHRONOUS (§A4) — the success dialog says it "can take up to 12 hours"; measured visibility ~24 s on a responsive Thor and &gt;90 s on a loaded one. Step 6 must POLL, and the active-class count does NOT increment immediately, so never assert count + 1.
 Teacher-side creation itself is already automated (ENTE / CREA modules, createNewClass.page.js) — what is NOT covered anywhere is this CROSS-ROLE journey, which is the point of the case.
 The teacher view groups by display name, so a school with a duplicate name is ambiguous here — pick a school with a UNIQUE name (§A5, TST_SADB_TC_6).</t>
   </si>
   <si>
+    <t>Not Automated</t>
+  </si>
+  <si>
+    <t>No automated coverage.</t>
+  </si>
+  <si>
     <t>TST_INVI_TC_12</t>
   </si>
   <si>
     <t>Verify clicking a notification opens its target and clears it from the unread count</t>
   </si>
   <si>
-    <t>#3 - Verify notifications</t>
-  </si>
-  <si>
     <t>Signed in as an administrator with at least one unread notification, the bell showing a count.</t>
   </si>
   <si>
-    <t>1. Record the unread badge count. 2. Open the notifications panel. 3. Click a notification whose target is known (e.g. a report-ready notification). 4. Confirm where it lands. 5. Re-open the panel and re-read the badge count and the item's read state.</t>
+    <t xml:space="preserve">1. Record the unread count from the bell's accessible name.
+2. Open the notifications panel.
+3. Click the OLDEST visible report-ready notification.
+4. Confirm where it lands.
+5. Re-read the unread count.</t>
   </si>
   <si>
     <t>An account with unread notifications; a report-ready notification if available.</t>
   </si>
   <si>
-    <t>The click navigates to the notification's target (a report-ready notification lands on the Reports tab), the item is marked read, and the unread badge count decreases by one. [ASSUMED]</t>
-  </si>
-  <si>
-    <t>Added 2026-09-01 from the other team's TC_GEN_003, whose steps click a notification and mark it read. All five of our notification cases (TST_INVI_TC_7-TC_11) are about rendering - badge, grouping, dates, wording - and none clicks a row. TST_INVI_TC_7 already pairs the badge with its accessible name, so this closes the loop by proving the count actually changes. Mutates state (read status is not reversible) - keep out of side-effect-free suites.</t>
+    <t>The click navigates to the notification's target (a report-ready notification lands on the Reports tab), the item is marked read, and the unread badge count decreases by one. `[ASSUMED]`</t>
+  </si>
+  <si>
+    <t>**[CORRECTED 2026-09-14 — live pass]** DECISION [user, 2026-09-14]: run on &lt;ADMIN_USER&gt; and accept consuming one unread notification per run (93 unread ≈ 90 runs); click the OLDEST visible report-ready row. Read the count before and after in the same run — never an absolute number. The landing destination is still [ASSUMED] (not grounded, because a click cannot be undone). — Superseded note follows: Added 2026-09-01 from the other team's TC_GEN_003, whose steps click a notification and mark it read. All five of our notification cases (`TST_INVI_TC_7`–`TC_11`) are about **rendering** — badge, grouping, dates, wording — and none clicks a row. `TST_INVI_TC_7` already pairs the badge with its accessible name, so this closes the loop by proving the count actually changes. **Mutates state** (read status is not reversible) — keep out of side-effect-free suites.</t>
+  </si>
+  <si>
+    <t>Written - not wired</t>
+  </si>
+  <si>
+    <t>Handler exists in adminNotifications.test.js but no execution file runs it.</t>
   </si>
   <si>
     <t>TST_LIBR_TC_34</t>
@@ -973,25 +1020,22 @@
     <t>Verify an MQA administrator does see the MQA/CQA restricted products</t>
   </si>
   <si>
-    <t>#5 - Verify non mqa admin should not see cqa/mqa product</t>
-  </si>
-  <si>
     <t>An MQA-provisioned administrator account with access to a school holding MQA/CQA products.</t>
   </si>
   <si>
     <t>1. Sign in as the MQA-provisioned administrator. 2. Open the school's Library tab. 3. Search for the restricted product by title and confirm it is listed.</t>
   </si>
   <si>
-    <t>MQA admin &lt;MQA_ADMIN_ACCOUNT&gt;; restricted product &lt;MQA_RESTRICTED_PRODUCT&gt;.</t>
-  </si>
-  <si>
-    <t>The MQA/CQA product is listed for the MQA administrator. [ASSUMED]</t>
-  </si>
-  <si>
-    <t>Added 2026-09-01 from the other team's TC_GEN_005, whose step 3 is an explicit control check. TST_LIBR_TC_32 proves only the negative half - that restricted products are hidden from a non-MQA admin - which a defect hiding the product from everyone would also satisfy. The pair is what makes either half meaningful. This is the same structural point as TST_CLST_TC_24 on the Classes tab: a negative-only assertion cannot distinguish correct behaviour from over-blocking.</t>
-  </si>
-  <si>
-    <t>Blocked at design time (skill rule 4): needs an MQA-provisioned administrator account, the counterpart to the non-MQA account TST_LIBR_TC_32 is already waiting on. Unblock both together - one fixture request covers the pair.</t>
+    <t>MQA admin `&lt;MQA_ADMIN_ACCOUNT&gt;`; restricted product `&lt;MQA_RESTRICTED_PRODUCT&gt;`.</t>
+  </si>
+  <si>
+    <t>The MQA/CQA product **is** listed for the MQA administrator. `[ASSUMED]`</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_GEN_005, whose step 3 is an explicit control check. `TST_LIBR_TC_32` proves only the negative half — that restricted products are hidden from a non-MQA admin — which a defect hiding the product from **everyone** would also satisfy. The pair is what makes either half meaningful. This is the same structural point as `TST_CLST_TC_24` on the Classes tab: a negative-only assertion cannot distinguish correct behaviour from over-blocking.</t>
+  </si>
+  <si>
+    <t>Blocked at design time (skill rule 4): needs an MQA-provisioned administrator account, the counterpart to the non-MQA account `TST_LIBR_TC_32` is already waiting on. Unblock both together — one fixture request covers the pair.</t>
   </si>
   <si>
     <t>TST_FOOT_TC_11</t>
@@ -1000,22 +1044,20 @@
     <t>Verify every admin footer link opens its intended destination</t>
   </si>
   <si>
-    <t>#8 - Verify footer link</t>
-  </si>
-  <si>
     <t>On any admin page with the footer visible.</t>
   </si>
   <si>
-    <t>1. Scroll to the footer and record every link it renders. 2. Click each link in turn. 3. Confirm the destination that opens and return. 4. Reconcile the set of links found against TST_FOOT_TC_10.</t>
-  </si>
-  <si>
-    <t>The footer links - the other team name Terms of use, Privacy notice, Accessibility, Our approach and FAQs.</t>
-  </si>
-  <si>
-    <t>Each footer link opens its intended destination and none is broken (no 404, no dead anchor). [ASSUMED]</t>
-  </si>
-  <si>
-    <t>Added 2026-09-01 from the other team's TC_GEN_008, which clicks each link and checks the destination. TST_FOOT_TC_10 asserts the footer renders seven links and omits Site Feedback - a presence check, not a navigation check. Reconcile the count while grounding: our register says seven links, theirs names five. One of the two is wrong; correct whichever it is and note the outcome here. Read-only, but links may open new tabs or external sites - handle that in automation.</t>
+    <t>1. Scroll to the footer and record every link it renders. 2. Click each link in turn. 3. Confirm the destination that opens and return. 4. Reconcile the set of links found against `TST_FOOT_TC_10`.</t>
+  </si>
+  <si>
+    <t>Admin footer links (7): Terms of use · Privacy notice · Accessibility · Our approach · FAQs · Cambridge One for schools · Help</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each internal footer link opens its page with no 404: Terms of use → /terms ("Terms of use"), Privacy notice → /privacy ("Privacy Notice"), Accessibility → /accessibility ("Accessibility on Cambridge One"), Cambridge One for schools → /institution-request.
+FAQs and Help both lead to the external help centre, and Our approach opens http://www.cambridge.org/english in a new tab.</t>
+  </si>
+  <si>
+    <t>**[CORRECTED 2026-09-14 — live pass]** Count RECONCILED: the admin footer renders SEVEN links — our register was right; the other team's five-link list is incomplete. Internal destinations VERIFIED live 2026-09-14. FAQs and Help point to the SAME external URL (a *helptest* host on Thor — environment-specific). "Our approach" has rel="nopener" — MISSPELT (should be noopener) — a minor security-hygiene defect. Logged-in internal hrefs are javascript:void(0): assert the resulting URL, never the href. — Superseded note follows: Added 2026-09-01 from the other team's TC_GEN_008, which clicks each link and checks the destination. `TST_FOOT_TC_10` asserts the footer **renders seven links and omits Site Feedback** — a presence check, not a navigation check. **Reconcile the count while grounding:** our register says seven links, theirs names five. One of the two is wrong; correct whichever it is and note the outcome here. **Read-only**, but links may open new tabs or external sites — handle that in automation.</t>
   </si>
   <si>
     <t>TST_SADB_TC_8</t>
@@ -1024,25 +1066,22 @@
     <t>Verify data stays scoped to the active organisation when an admin manages several schools</t>
   </si>
   <si>
-    <t>#11 - Verify different tab navigation</t>
-  </si>
-  <si>
-    <t>An administrator with access to two or more schools, where each school holds at least one record (class, student, staff member, library product) that exists only in that school.</t>
-  </si>
-  <si>
-    <t>1. Sign in as the multi-org administrator and open school A. 2. On each tab - Classes, Students, Staff, Library - confirm every listed record belongs to school A, and specifically that school B's unique records are absent. 3. Switch to school B and repeat in the opposite direction. 4. Apply a search or filter in school A, then switch to school B, and confirm no results carry across.</t>
-  </si>
-  <si>
-    <t>Multi-org admin &lt;MULTI_ORG_ADMIN&gt;; unique records &lt;A_ONLY_RECORD&gt; and &lt;B_ONLY_RECORD&gt;.</t>
-  </si>
-  <si>
-    <t>Every tab shows only the active organisation's data. No record unique to the other school appears anywhere, and switching organisations does not carry search or filter results across. [ASSUMED]</t>
-  </si>
-  <si>
-    <t>Added 2026-09-01 from the other team's TC_ORG_001, whose expected result ends "with no cross-org data leakage". TST_SADB_TC_3 proves each organisation loads independently; it does not prove one cannot see the other's data. Highest-severity gap of the entire comparison - a leak here is a data-privacy incident, not a UI defect, which is why this is High priority despite sitting in a thinly covered area. Step 4 exists because carried-over query state is the most likely mechanism for a leak.</t>
-  </si>
-  <si>
-    <t>Blocked at design time (skill rule 4): needs a multi-organisation admin fixture with records unique to each school, so that absence is provable rather than assumed. Unblock by provisioning two small schools under one admin with deliberately distinct data. NOTE: the multi-organisation area has no register of its own - if it grows beyond the SADB cases it should get one (see the 2026-09-01 handoff).</t>
+    <t>An administrator with access to two or more schools, where each school holds at least one record (class, student, staff member, library product) that exists **only** in that school.</t>
+  </si>
+  <si>
+    <t>1. Sign in as the multi-org administrator and open school A. 2. On each tab — Classes, Students, Staff, Library — confirm every listed record belongs to school A, and specifically that school B's unique records are **absent**. 3. Switch to school B and repeat in the opposite direction. 4. Apply a search or filter in school A, then switch to school B, and confirm no results carry across.</t>
+  </si>
+  <si>
+    <t>Multi-org admin `&lt;MULTI_ORG_ADMIN&gt;`; unique records `&lt;A_ONLY_RECORD&gt;` and `&lt;B_ONLY_RECORD&gt;`.</t>
+  </si>
+  <si>
+    <t>Every tab shows only the active organisation's data. No record unique to the other school appears anywhere, and switching organisations does not carry search or filter results across. `[ASSUMED]`</t>
+  </si>
+  <si>
+    <t>Added 2026-09-01 from the other team's TC_ORG_001, whose expected result ends "with no cross-org data leakage". `TST_SADB_TC_3` proves each organisation **loads** independently; it does not prove one cannot see the other's data. **Highest-severity gap of the entire comparison** — a leak here is a data-privacy incident, not a UI defect, which is why this is High priority despite sitting in a thinly covered area. Step 4 exists because carried-over query state is the most likely mechanism for a leak.</t>
+  </si>
+  <si>
+    <t>Blocked at design time (skill rule 4): needs a multi-organisation admin fixture with records unique to each school, so that absence is provable rather than assumed. Unblock by provisioning two small schools under one admin with deliberately distinct data. NOTE: the multi-organisation area has no register of its own — if it grows beyond the SADB cases it should get one (see the 2026-09-01 handoff).</t>
   </si>
 </sst>
 </file>
@@ -1434,7 +1473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:P42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1452,7 +1491,7 @@
     <col min="14" max="14" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1495,1809 +1534,2061 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="N3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="N9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O9" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="P9" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>154</v>
+        <v>182</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D27" s="2" t="s">
+      <c r="N27" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="P27" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="N27" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>222</v>
-      </c>
       <c r="E35" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>258</v>
+        <v>93</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>266</v>
+        <v>189</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>275</v>
+        <v>154</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>283</v>
+        <v>134</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>289</v>
+        <v>299</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Generic/AdminApp_Generic_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Generic/AdminApp_Generic_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="220">
   <si>
     <t>S.No.</t>
   </si>
@@ -102,7 +102,7 @@
     <t>Automated</t>
   </si>
   <si>
-    <t>Suite: adminGeneric | 2026-09-16: Pass across 2 runs</t>
+    <t>Suite: adminGeneric | Not executed in this audit - status carried over, treat as unverified</t>
   </si>
   <si>
     <t>TST_ASHL_TC_2</t>
@@ -219,108 +219,6 @@
   </si>
   <si>
     <t>⚠️ EXPECTED RESULT NOT VERIFIED — the edit-then-leave path was not exercised. Specifically UNKNOWN: whether an unsaved-changes confirmation appears. admin-shared.md §A6 records a pre-rendered "Save changes?" dialog on the OTHER app's Manage learner profile, and the create-classes form auto-saves a draft (§A4) — so BOTH "silently discards" and "prompts" are plausible here. Do not assume; capture what happens. Back qid "c-mp-btn-1". CHANGES ACCOUNT STATE only if Update is pressed, which this case avoids.</t>
-  </si>
-  <si>
-    <t>TST_MYPR_TC_5</t>
-  </si>
-  <si>
-    <t>Verify an over-long first name is handled correctly when no client-side limit exists</t>
-  </si>
-  <si>
-    <t>Edge</t>
-  </si>
-  <si>
-    <t>Logged in as school-admin &lt;ADMIN_USER&gt; on Thor; "My school accounts" (/admin/admin/dashboard) displayed. Manage profile open on the "Personal info" tab. USE A DISPOSABLE ACCOUNT.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Clear "First name".
-2. Type a 300-character value.
-3. Observe whether the field truncates the input as it is typed.
-4. Click "Update".</t>
-  </si>
-  <si>
-    <t>First name: 300 repetitions of "a"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">After step 3 the field accepts all 300 characters — there is NO client-side truncation.
-[ASSUMED] After step 4 the server rejects the value with a validation message, or accepts and truncates it. Capture which, and the exact message.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED PARTIALLY 2026-08-27: the ABSENCE of a limit is verified — ALL SEVEN fields across both tabs have maxlength=null and none is marked required. What the SERVER does is [ASSUMED]. This is a deliberate departure from the rest of the admin app, where limits are declared and enforced client-side (class name 50, grading scale title 20 — admin-shared.md §A3). Because nothing is declared here, boundary cases CANNOT be derived from the markup and must be found by submitting. ⚠️ DO NOT RUN ON &lt;ADMIN_USER&gt; — that account is the login for the whole admin suite. Blocked until a disposable account exists.</t>
-  </si>
-  <si>
-    <t>Not Run</t>
-  </si>
-  <si>
-    <t>Excluded - Phase 1</t>
-  </si>
-  <si>
-    <t>Out of Phase 1 automation scope.</t>
-  </si>
-  <si>
-    <t>TST_MYPR_TC_6</t>
-  </si>
-  <si>
-    <t>Verify an error is shown when the new password and its confirmation do not match</t>
-  </si>
-  <si>
-    <t>Negative</t>
-  </si>
-  <si>
-    <t>Logged in as school-admin &lt;ADMIN_USER&gt; on Thor; "My school accounts" (/admin/admin/dashboard) displayed. Manage profile open on the "Password" tab. USE A DISPOSABLE ACCOUNT.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Enter the correct current password in "Old password".
-2. Enter a valid new password in "New password".
-3. Enter a DIFFERENT value in "Confirm new password".
-4. Click "Update".</t>
-  </si>
-  <si>
-    <t>Old: &lt;VALID_PASSWORD&gt; · New: "Compro@2026" · Confirm: "Compro@2027"</t>
-  </si>
-  <si>
-    <t>[ASSUMED] The password is NOT changed and a mismatch validation message is shown against the confirmation field.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. ⚠️ ERROR COPY NOT CAPTURED — nothing was submitted, by agreement, because &lt;ADMIN_USER&gt; is the admin suite's login account. The message text must be captured on a disposable account. For reference the equivalent page in the other app exposes a dedicated error element ("confirmPasswordError_text" in the SETT selector set), so a field-level message is expected here too — but that is the OTHER app and must not be assumed identical. DESTRUCTIVE IF IT SUCCEEDS: a mistyped variant of this case would change a real password.</t>
-  </si>
-  <si>
-    <t>TST_MYPR_TC_7</t>
-  </si>
-  <si>
-    <t>Verify an error is shown when the old password is incorrect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Enter an INCORRECT value in "Old password".
-2. Enter a valid new password in both "New password" and "Confirm new password".
-3. Click "Update".</t>
-  </si>
-  <si>
-    <t>Old: "WrongPassword123" · New / Confirm: "Compro@2026"</t>
-  </si>
-  <si>
-    <t>[ASSUMED] The password is NOT changed and an error identifies the old password as incorrect.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. ⚠️ ERROR COPY NOT CAPTURED — see TST_MYPR_TC_6. The SETT selector set has a matching "currentPasswordError_text" element in the other app. Worth checking whether repeated failures lock the account, which would affect suite design.</t>
-  </si>
-  <si>
-    <t>TST_MYPR_TC_8</t>
-  </si>
-  <si>
-    <t>Verify the active profile tab is identifiable to assistive technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Inspect the "Personal info" and "Password" tab controls.
-2. Check for a tab role and a selected-state attribute.
-3. Switch tabs and re-check.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each tab exposes an appropriate role and a selected state, so assistive technology can announce which tab is active.
-ACTUAL (2026-08-27): this FAILS. Both are plain &lt;a&gt; elements with NO role="tab" and NO aria-selected. Nothing in the markup or the URL identifies the active tab.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. Raised as a case because it is both an accessibility gap and an automation blocker: with no aria-selected AND no URL change between tabs (TST_MYPR_TC_3), there is no attribute to assert the active tab on — automation must fall back to checking which fields are visible. Confirm with the product team whether this should be raised as a defect. Tab qids "c-mp-tab-1" (Personal info) and "c-mp-tab-2" (Password).</t>
   </si>
   <si>
     <t>TST_INVI_TC_7</t>
@@ -374,6 +272,9 @@
     <t>Verify the panel renders only the five most recent notifications when many are unread</t>
   </si>
   <si>
+    <t>Edge</t>
+  </si>
+  <si>
     <t>Logged in as school-admin &lt;ADMIN_USER&gt; on Thor; "My school accounts" (/admin/admin/dashboard) displayed. The account has many unread notifications (92 at capture).</t>
   </si>
   <si>
@@ -415,6 +316,9 @@
   </si>
   <si>
     <t>Verify report-ready notifications describe the Reports destination consistently</t>
+  </si>
+  <si>
+    <t>Negative</t>
   </si>
   <si>
     <t>Low</t>
@@ -477,80 +381,6 @@
     <t>Titles grounded live 2026-08-27 from the pre-rendered DOM. ⚠️ All five share the SINGLE qid "cHeader-hlp-6" — when automated they must be addressed by text or index, never by qid. Same trap class as "t-prd-cmp-cntr-1" (admin-shared.md §B3), and the same shape as the cFooter-9 duplication the footer selectors already work around with an aria-label qualifier. What each topic OPENS was not captured — [ASSUMED] and out of scope for this case.</t>
   </si>
   <si>
-    <t>TST_ASHL_TC_5</t>
-  </si>
-  <si>
-    <t>Verify all five school tabs are shown with Classes active when a school is opened</t>
-  </si>
-  <si>
-    <t>#11 — Verify different tab navigation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click a school card on "My school accounts".
-2. Observe the tab strip and which tab is active.
-3. Observe the page heading and the browser tab title.</t>
-  </si>
-  <si>
-    <t>School: "3 July Test School 1" (&lt;SCHOOL_KEY&gt;)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exactly FIVE tabs are shown, in this order and in upper case:
-CLASSES · STUDENTS · STAFF · LIBRARY · REPORTS
-"CLASSES" is the active tab by default, the page heading shows the school name, and the browser tab reads "Classes | Cambridge One".</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. Tab qids "aDetail-1" (Classes), "aDetail-2" (Students), "aDetail-4" (Staff), "aDetail-5" (Library), "aDetail-6" (Reports). ⚠️ "aDetail-3" IS SKIPPED — the sequence is 1,2,4,5,6. Do not iterate 1..5 assuming contiguity. ⚠️ THE ACTIVE MARKER IS ON THE PARENT &lt;li&gt;, not the anchor: "li.nav-item.active &gt; a". The anchor className is identical on every tab whether active or not, so asserting on the link class is a guaranteed false green. Labels render UPPER CASE — confirm whether that is CSS text-transform or the actual text before asserting case-sensitively.</t>
-  </si>
-  <si>
-    <t>TST_ASHL_TC_6</t>
-  </si>
-  <si>
-    <t>Verify each tab loads its own page and becomes the active tab when it is selected</t>
-  </si>
-  <si>
-    <t>Logged in as school-admin &lt;ADMIN_USER&gt; on Thor; "My school accounts" (/admin/admin/dashboard) displayed. A school is open on the Classes tab.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click "STUDENTS" and note the URL, title and active tab.
-2. Repeat for "STAFF", "LIBRARY", "REPORTS", then "CLASSES".</t>
-  </si>
-  <si>
-    <t>School slug: org_&lt;SCHOOL_SLUG&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each tab navigates to its own URL, sets its own browser-tab title, and becomes the active tab:
-| Tab | URL suffix | Title |
-| CLASSES | /class | "Classes \| Cambridge One" |
-| STUDENTS | /learner | "Students \| Cambridge One" |
-| STAFF | /staff | "Staff \| Cambridge One" |
-| LIBRARY | /library | "Library \| Cambridge One" |
-| REPORTS | /reports | "Reports \| Cambridge One" |
-The school heading stays unchanged throughout.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27 — all five walked and every URL and title confirmed. ⚠️ NOTE the STUDENTS tab routes to "/learner", NOT "/student". A URL assertion built from the tab label will fail on this one. Tabs carry REAL hrefs (unlike the footer, whose logged-in hrefs collapse to javascript:void(0) — TST_FOOT_TC_10 remarks), so tab navigation is genuinely href-driven. TIMING measured this session: Reports took ~4.3 s to become active, Classes ~1.2 s. Poll for "li.nav-item.active &gt; a" carrying the expected qid rather than using a fixed pause (admin-shared.md §B8).</t>
-  </si>
-  <si>
-    <t>TST_ASHL_TC_7</t>
-  </si>
-  <si>
-    <t>Verify the active school tab is identifiable to assistive technology</t>
-  </si>
-  <si>
-    <t>Logged in as school-admin &lt;ADMIN_USER&gt; on Thor; "My school accounts" (/admin/admin/dashboard) displayed. A school is open.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Inspect each tab link for an aria-current or selected-state attribute.
-2. Switch tabs and re-inspect.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The active tab exposes an accessible current/selected state, so assistive technology can announce which section the user is in.
-ACTUAL (2026-08-27): this FAILS. No tab link carries aria-current or aria-selected; the only indicator is the "active" CSS class on the parent &lt;li&gt;, which is presentational.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. This is the SECOND instance of the same gap in this batch — the My Profile tabs have it too (TST_MYPR_TC_8). Worth raising as one combined accessibility ticket rather than two. The school tabs are at least recoverable for automation via "li.nav-item.active"; the profile tabs have no indicator at all, which makes them the more severe of the two.</t>
-  </si>
-  <si>
     <t>TST_FOOT_TC_10</t>
   </si>
   <si>
@@ -711,34 +541,13 @@
     <t>BLOCKED at design time 2026-08-27 on TWO counts: (1) no non-MQA admin account is available — &lt;ADMIN_USER&gt;'s home school IS MQA Sierra School (MQA-ABC-DEF); (2) the product team must first define what technically marks a product as MQA/CQA-restricted. Unblock with a non-MQA admin account and that definition.</t>
   </si>
   <si>
-    <t>TST_SADB_TC_2</t>
-  </si>
-  <si>
-    <t>Verify every school the administrator manages is listed when My school accounts is opened</t>
+    <t>TST_SADB_TC_3</t>
+  </si>
+  <si>
+    <t>Verify switching between organisations loads each one independently when the admin manages several</t>
   </si>
   <si>
     <t>#10 — Admin part of multiple org</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Observe the "My school accounts" page.
-2. Inspect each school card.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every school the administrator manages is listed, one card each, numbered sequentially from "01" with zero padding.
-Each card shows: index, school name, address, the label "School key", the key itself in XXX-XXX-XXX format, a "Copy" control, and a chevron opening the school.
-Observed 2026-08-27 for &lt;ADMIN_USER&gt;: 7 schools, numbered 01–07.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. Card qid "aDashboard-N" (a.inst-link); chevron is a SEPARATE "aDashboard1-N". Both are POSITIONAL. The school key is carried in the card's aria-label, which is what makes key-based selection possible (schoolAdminDashboard.schoolLinkByKey uses a.inst-link[aria-label*="{{key}}"]).
-⚠️ NEVER assert the literal count 7 — this is a shared account and the list changes (admin-shared.md §A5). Assert the card STRUCTURE and that the expected key is present.
-Extends the existing SADB module (TST_SADB_TC_1 opens a school by key) — that case already covers opening; this one covers the LISTING, which nothing did.
-⚠️ EXTENDS admin-shared.md §0, which documents 4 schools. This account sees 7 — KNF-XRD-QVE, HQC-ZWM-ZVF and GYB-JMU-KYA were undocumented.</t>
-  </si>
-  <si>
-    <t>TST_SADB_TC_3</t>
-  </si>
-  <si>
-    <t>Verify switching between organisations loads each one independently when the admin manages several</t>
   </si>
   <si>
     <t xml:space="preserve">1. Open the first school and note the org slug in the URL and the page heading.
@@ -757,31 +566,6 @@
 ⚠️ The org slug is NOT derivable from the school name or key — "3 July Test School 1" (FCN-CHZ-PDA) maps to org_perf_testschool_1. Capture each slug; never construct it.
 The school context MUST be set by clicking the card — deep-linking /admin/admin/org_&lt;slug&gt;/class returns /dashboard/error even when authenticated (admin-shared.md §A1).
 Worth checking whether the per-account server-side class Filter and Search (§A4) are scoped per school or leak across organisations — that is unknown and would be a real defect if they leak.</t>
-  </si>
-  <si>
-    <t>TST_SADB_TC_4</t>
-  </si>
-  <si>
-    <t>Verify two schools sharing a display name remain distinguishable by their school key</t>
-  </si>
-  <si>
-    <t>#12 — Verify viewing multiple schools</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate the two cards sharing the same display name.
-2. Compare their school keys.
-3. Open the one matching a specific key and confirm which school loaded.</t>
-  </si>
-  <si>
-    <t>Duplicate display name "3 July Test School 1" — keys FCN-CHZ-PDA and ZPB-TWP-AEQ</t>
-  </si>
-  <si>
-    <t>Both cards show the SAME display name but DIFFERENT school keys, and the card selected by key opens that specific school.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27 — cards 01 and 02 both read "3 July Test School 1" with keys FCN-CHZ-PDA and ZPB-TWP-AEQ, and identical addresses too.
-⚠️ THIS IS THE CASE THAT JUSTIFIES admin-shared.md §0's standing rule: ALWAYS select a school by KEY, never by name or card position. Selecting by name is ambiguous here, and card qids (aDashboard-N) are positional so they re-issue when the list changes.
-Confirming WHICH school loaded (step 3) needs a distinguishing feature — the org slug in the URL is the reliable one, since the heading shows the shared name.</t>
   </si>
   <si>
     <t>TST_SRQS_TC_2</t>
@@ -839,66 +623,6 @@
     <t>**[CORRECTED 2026-09-14 — live pass]** VERIFIED LIVE 2026-09-14 — walked to the summary, never submitted. Next is NATIVELY disabled (disabled attribute + .disabled + pointer-events none), so an isEnabled assertion is valid. The wizard advances IN-PAGE (URL never changes) and the Next qid differs per step. ⚠️ The existing wizard modules' generic "button.btn-purple" also matches "Send Request" (t-ss-as-btn-1) — stop by qid. The summary omits school type and number of teachers. — Superseded note follows: ⚠️ EXPECTED RESULT NOT VERIFIED — the wizard was not walked in this session. INFERRED from the existing automation, whose case titles state the enabling direction only, e.g. TST_SCTY_TC_3 "Select first radio option (Primary school) to ENABLE Next button" and TST_SNAM_TC_3 "Fill school name field to ENABLE Next button". The DISABLED half is nowhere asserted, which is the gap this case fills. Confirm whether Next is natively disabled or only CSS-disabled — admin-shared.md §B4 records CSS-only disabling elsewhere in this app, which would make a naive enabled-state check a false green. SIDE-EFFECT FREE: stops short of submission.</t>
   </si>
   <si>
-    <t>TST_ASHL_TC_8</t>
-  </si>
-  <si>
-    <t>Verify no dialog is visible when an admin screen first loads</t>
-  </si>
-  <si>
-    <t>#9 — Verify various errors in forms and modals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Load the Classes tab and observe the screen without interacting.
-2. Repeat for Students, Staff, Library and Reports.</t>
-  </si>
-  <si>
-    <t>On every tab, no dialog, warning or error is visible on load. The screen shows only its own content.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27 — verified that every dialog present in the DOM was hidden on load (Classes 5, Students 4, Staff 1; all offsetParent === null). ⚠️ THIS IS THE HEADLINE AUTOMATION TRAP FOR THIS SCENARIO. Admin dialogs are PRE-RENDERED, so they exist in the DOM before anything triggers them. Any check of the form "getElementCount(dialog) &gt; 0" therefore passes ALWAYS and proves nothing — admin-shared.md §B2 records this silently breaking reset_filters for weeks. Assert VISIBILITY, never presence. Note also that opacity:0 still counts as visible to Playwright; only display:none is hidden.</t>
-  </si>
-  <si>
-    <t>TST_ASHL_TC_9</t>
-  </si>
-  <si>
-    <t>Verify the 50-item limit warnings use a consistent message pattern across screens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Read the bulk-limit warning offered on the Classes tab.
-2. Read the equivalent warning on the Students tab.
-3. Compare their wording.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Both follow the same two-line pattern, differing only in the noun:
-Classes: "You can only delete 50 classes at one time" / "Please uncheck some classes to continue"
-Students: "You can only remove 50 students at one time" / "Please uncheck some students to continue"
-Both offer a "Close" control.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. COPY GROUNDED LIVE 2026-08-27 — both captured VERBATIM from the pre-rendered DOM (§A6) without reaching the capped state, which would otherwise require 51+ rows. Note the VERB differs with the domain — "delete" for classes, "remove" for students — so a single shared assertion string is wrong. The LIMIT (50) and the sentence shape are the consistent parts. Reaching these states for real is Blocked on the shared school (admin-shared.md §A5: it holds 26 students, so the 50-student cap cannot be hit).</t>
-  </si>
-  <si>
-    <t>TST_ASHL_TC_10</t>
-  </si>
-  <si>
-    <t>Verify destructive confirmations state their consequence before the action is taken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Read the class-deletion confirmation.
-2. Read the student-removal confirmation.
-3. Read the change-school-key confirmation.
-4. Check each offers a way to back out.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each destructive confirmation names its consequence and offers a non-destructive exit:
-Class delete — "WARNING!" / "There might be students, teachers and course materials in the selected classes" / "Are you sure you want to delete?" / "No, cancel"
-Student removal — "I confirm that I want to remove students from my school account" / "Cancel" / "Request to remove"
-Change school key — "CAREFUL!" / "Changing the school key cannot be undone" / "Cancel"</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. ALL THREE CAPTURED VERBATIM 2026-08-27 from the pre-rendered DOM, without triggering any of them — which is the only safe way, since all three are destructive on a shared school. ⚠️ The change-school-key dialog is present on EVERY admin tab (Classes, Students, Staff all carry it) because School settings lives in the shared page chrome — scope any modal selector with :has(...) to the specific dialog, or it will match this one everywhere. Async follow-ups are also pre-rendered and worth checking in the same pass: "This will take a few minutes" (classes) and "Removing students may take some time" (students).</t>
-  </si>
-  <si>
     <t>TST_SADB_TC_5</t>
   </si>
   <si>
@@ -920,28 +644,6 @@
   </si>
   <si>
     <t>**[CORRECTED 2026-09-14 — live pass]** Toggling back returns to the admin page the round trip STARTED on (verified from /class on 2026-09-14), so start this case on the dashboard. Do NOT assert the document title — it varies with the load path ("Administrator | Cambridge One" vs "My school accounts | Cambridge One"). — Superseded note follows: GROUNDED LIVE 2026-08-27 — the full round trip was performed and the account was left in Administrator view. ⚠️ THE SWITCH ELEMENT IS NAMED DIFFERENTLY IN EACH VIEW: ".can-toggle__switch" (double underscore) in the admin view, ".can-toggle-switch" (single hyphen) in the teacher view. A selector written for one view SILENTLY FAILS to find it in the other, which breaks exactly the round trip this case exercises. Use "#teacher-admin-toggle" (stable in both) and read the input's checked state — false = Administrator, true = Teacher. The focusable control is the inner [tabindex="0"] div; the input itself is aria-hidden. The toggle also appears on inner admin tabs, not just the dashboard. Existing selector schoolAdminDashboard.teacherAdminToggle already targets the input; this extends SADB. SIDE-EFFECT FREE — a view switch only.</t>
-  </si>
-  <si>
-    <t>TST_SADB_TC_6</t>
-  </si>
-  <si>
-    <t>Verify the teacher view lists the schools where the user teaches, not those they administer</t>
-  </si>
-  <si>
-    <t>Logged in as school-admin &lt;ADMIN_USER&gt; on Thor; "My school accounts" (/admin/admin/dashboard) displayed. The user is both an administrator and a teacher on overlapping sets of schools.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. On "My school accounts", list the schools shown.
-2. Switch to the teacher view.
-3. List the school groups shown there.
-4. Compare the two lists.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The two lists are NOT the same. The administrator view shows schools the user administers; the teacher view groups classes under schools where the user teaches, which may include schools absent from the administrator view.
-Observed 2026-08-27: administrator view 7 schools; teacher view 8 school groups, including "ABERYSTWYTH COLLEGE : THOR" and "LTI INTEGRATIONS TEST2", neither of which appears in the administrator list.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. This matters because it is easy to assume the two views show the same estate — they do not, and a test asserting equal school counts across the toggle will fail. ⚠️ The teacher view groups by school DISPLAY NAME, so the two distinct schools both called "3 July Test School 1" (FCN-CHZ-PDA and ZPB-TWP-AEQ) collapse into a SINGLE group there. The admin view keeps them separate via their keys. Do not match schools across the two views by name. ⚠️ NEVER assert the literal counts 7 and 8 — shared account (§A5). Assert the RELATIONSHIP: the teacher list contains at least one school the admin list does not. ⚠️ Every "Create class" button in the teacher view shares qid "tDashboard-ncls-btn-1" — 7 elements, one per school group. See TST_SADB_TC_7.</t>
   </si>
   <si>
     <t>TST_SADB_TC_7</t>
@@ -977,6 +679,9 @@
 The teacher view groups by display name, so a school with a duplicate name is ambiguous here — pick a school with a UNIQUE name (§A5, TST_SADB_TC_6).</t>
   </si>
   <si>
+    <t>Not Run</t>
+  </si>
+  <si>
     <t>Not Automated</t>
   </si>
   <si>
@@ -1064,6 +769,9 @@
   </si>
   <si>
     <t>Verify data stays scoped to the active organisation when an admin manages several schools</t>
+  </si>
+  <si>
+    <t>#11 — Verify different tab navigation</t>
   </si>
   <si>
     <t>An administrator with access to two or more schools, where each school holds at least one record (class, student, staff member, library product) that exists **only** in that school.</t>
@@ -1473,7 +1181,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P42"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1843,7 +1551,7 @@
     </row>
     <row r="8" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>61</v>
@@ -1852,157 +1560,157 @@
         <v>62</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="L8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>75</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>74</v>
@@ -2011,69 +1719,69 @@
         <v>56</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>26</v>
@@ -2093,16 +1801,16 @@
     </row>
     <row r="13" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>19</v>
@@ -2114,16 +1822,16 @@
         <v>21</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>26</v>
@@ -2143,37 +1851,37 @@
     </row>
     <row r="14" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>56</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>26</v>
@@ -2193,37 +1901,37 @@
     </row>
     <row r="15" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>56</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>26</v>
@@ -2243,37 +1951,37 @@
     </row>
     <row r="16" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>26</v>
@@ -2293,16 +2001,16 @@
     </row>
     <row r="17" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>19</v>
@@ -2311,19 +2019,19 @@
         <v>20</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>26</v>
@@ -2343,57 +2051,57 @@
     </row>
     <row r="18" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>21</v>
+        <v>124</v>
       </c>
       <c r="H18" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M18" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="I18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J18" s="2" t="s">
+      <c r="N18" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="O18" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="P18" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>132</v>
@@ -2402,16 +2110,16 @@
         <v>133</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>20</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>135</v>
@@ -2429,21 +2137,21 @@
         <v>26</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>139</v>
@@ -2452,178 +2160,178 @@
         <v>140</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>20</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>26</v>
+        <v>147</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>71</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
+        <v>28</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="G21" s="2" t="s">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>23</v>
+        <v>152</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>21</v>
+        <v>158</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>26</v>
+        <v>163</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>29</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>26</v>
@@ -2643,16 +2351,16 @@
     </row>
     <row r="24" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>19</v>
@@ -2661,19 +2369,19 @@
         <v>20</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>26</v>
@@ -2693,16 +2401,16 @@
     </row>
     <row r="25" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>19</v>
@@ -2711,884 +2419,234 @@
         <v>20</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>178</v>
+        <v>26</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="I26" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M26" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="J26" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="N26" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>28</v>
+        <v>194</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>29</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>189</v>
+        <v>141</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>177</v>
+        <v>129</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>177</v>
+        <v>129</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>179</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>198</v>
+        <v>106</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>21</v>
+        <v>206</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>23</v>
+        <v>208</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>21</v>
+        <v>214</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="N30" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="P30" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
-        <v>30</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="N31" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="O31" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="P31" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
-        <v>31</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N32" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P32" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
-        <v>32</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="N33" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O33" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="P33" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
-        <v>33</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="N34" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O34" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="P34" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
-        <v>34</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="N35" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="P35" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
-        <v>35</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N36" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P36" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
-        <v>36</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M37" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="N37" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O37" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="P37" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
-        <v>37</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
-        <v>38</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="N39" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O39" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="P39" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
-        <v>39</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="O40" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="P40" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
-        <v>40</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M41" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O41" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P41" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="P42" s="2" t="s">
-        <v>179</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Generic/AdminApp_Generic_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Generic/AdminApp_Generic_test_cases.xlsx
@@ -102,7 +102,7 @@
     <t>Automated</t>
   </si>
   <si>
-    <t>Suite: adminGeneric | Not executed in this audit - status carried over, treat as unverified</t>
+    <t>Suite: adminGeneric | 2026-09-16: Pass across 2 runs</t>
   </si>
   <si>
     <t>TST_ASHL_TC_2</t>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Generic/AdminApp_Generic_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Generic/AdminApp_Generic_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="220">
   <si>
     <t>S.No.</t>
   </si>
@@ -219,108 +219,6 @@
   </si>
   <si>
     <t>⚠️ EXPECTED RESULT NOT VERIFIED — the edit-then-leave path was not exercised. Specifically UNKNOWN: whether an unsaved-changes confirmation appears. admin-shared.md §A6 records a pre-rendered "Save changes?" dialog on the OTHER app's Manage learner profile, and the create-classes form auto-saves a draft (§A4) — so BOTH "silently discards" and "prompts" are plausible here. Do not assume; capture what happens. Back qid "c-mp-btn-1". CHANGES ACCOUNT STATE only if Update is pressed, which this case avoids.</t>
-  </si>
-  <si>
-    <t>TST_MYPR_TC_5</t>
-  </si>
-  <si>
-    <t>Verify an over-long first name is handled correctly when no client-side limit exists</t>
-  </si>
-  <si>
-    <t>Edge</t>
-  </si>
-  <si>
-    <t>Logged in as school-admin &lt;ADMIN_USER&gt; on Thor; "My school accounts" (/admin/admin/dashboard) displayed. Manage profile open on the "Personal info" tab. USE A DISPOSABLE ACCOUNT.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Clear "First name".
-2. Type a 300-character value.
-3. Observe whether the field truncates the input as it is typed.
-4. Click "Update".</t>
-  </si>
-  <si>
-    <t>First name: 300 repetitions of "a"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">After step 3 the field accepts all 300 characters — there is NO client-side truncation.
-[ASSUMED] After step 4 the server rejects the value with a validation message, or accepts and truncates it. Capture which, and the exact message.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED PARTIALLY 2026-08-27: the ABSENCE of a limit is verified — ALL SEVEN fields across both tabs have maxlength=null and none is marked required. What the SERVER does is [ASSUMED]. This is a deliberate departure from the rest of the admin app, where limits are declared and enforced client-side (class name 50, grading scale title 20 — admin-shared.md §A3). Because nothing is declared here, boundary cases CANNOT be derived from the markup and must be found by submitting. ⚠️ DO NOT RUN ON &lt;ADMIN_USER&gt; — that account is the login for the whole admin suite. Blocked until a disposable account exists.</t>
-  </si>
-  <si>
-    <t>Not Run</t>
-  </si>
-  <si>
-    <t>Excluded - Phase 1</t>
-  </si>
-  <si>
-    <t>Out of Phase 1 automation scope.</t>
-  </si>
-  <si>
-    <t>TST_MYPR_TC_6</t>
-  </si>
-  <si>
-    <t>Verify an error is shown when the new password and its confirmation do not match</t>
-  </si>
-  <si>
-    <t>Negative</t>
-  </si>
-  <si>
-    <t>Logged in as school-admin &lt;ADMIN_USER&gt; on Thor; "My school accounts" (/admin/admin/dashboard) displayed. Manage profile open on the "Password" tab. USE A DISPOSABLE ACCOUNT.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Enter the correct current password in "Old password".
-2. Enter a valid new password in "New password".
-3. Enter a DIFFERENT value in "Confirm new password".
-4. Click "Update".</t>
-  </si>
-  <si>
-    <t>Old: &lt;VALID_PASSWORD&gt; · New: "Compro@2026" · Confirm: "Compro@2027"</t>
-  </si>
-  <si>
-    <t>[ASSUMED] The password is NOT changed and a mismatch validation message is shown against the confirmation field.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. ⚠️ ERROR COPY NOT CAPTURED — nothing was submitted, by agreement, because &lt;ADMIN_USER&gt; is the admin suite's login account. The message text must be captured on a disposable account. For reference the equivalent page in the other app exposes a dedicated error element ("confirmPasswordError_text" in the SETT selector set), so a field-level message is expected here too — but that is the OTHER app and must not be assumed identical. DESTRUCTIVE IF IT SUCCEEDS: a mistyped variant of this case would change a real password.</t>
-  </si>
-  <si>
-    <t>TST_MYPR_TC_7</t>
-  </si>
-  <si>
-    <t>Verify an error is shown when the old password is incorrect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Enter an INCORRECT value in "Old password".
-2. Enter a valid new password in both "New password" and "Confirm new password".
-3. Click "Update".</t>
-  </si>
-  <si>
-    <t>Old: "WrongPassword123" · New / Confirm: "Compro@2026"</t>
-  </si>
-  <si>
-    <t>[ASSUMED] The password is NOT changed and an error identifies the old password as incorrect.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. ⚠️ ERROR COPY NOT CAPTURED — see TST_MYPR_TC_6. The SETT selector set has a matching "currentPasswordError_text" element in the other app. Worth checking whether repeated failures lock the account, which would affect suite design.</t>
-  </si>
-  <si>
-    <t>TST_MYPR_TC_8</t>
-  </si>
-  <si>
-    <t>Verify the active profile tab is identifiable to assistive technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Inspect the "Personal info" and "Password" tab controls.
-2. Check for a tab role and a selected-state attribute.
-3. Switch tabs and re-check.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each tab exposes an appropriate role and a selected state, so assistive technology can announce which tab is active.
-ACTUAL (2026-08-27): this FAILS. Both are plain &lt;a&gt; elements with NO role="tab" and NO aria-selected. Nothing in the markup or the URL identifies the active tab.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. Raised as a case because it is both an accessibility gap and an automation blocker: with no aria-selected AND no URL change between tabs (TST_MYPR_TC_3), there is no attribute to assert the active tab on — automation must fall back to checking which fields are visible. Confirm with the product team whether this should be raised as a defect. Tab qids "c-mp-tab-1" (Personal info) and "c-mp-tab-2" (Password).</t>
   </si>
   <si>
     <t>TST_INVI_TC_7</t>
@@ -374,6 +272,9 @@
     <t>Verify the panel renders only the five most recent notifications when many are unread</t>
   </si>
   <si>
+    <t>Edge</t>
+  </si>
+  <si>
     <t>Logged in as school-admin &lt;ADMIN_USER&gt; on Thor; "My school accounts" (/admin/admin/dashboard) displayed. The account has many unread notifications (92 at capture).</t>
   </si>
   <si>
@@ -415,6 +316,9 @@
   </si>
   <si>
     <t>Verify report-ready notifications describe the Reports destination consistently</t>
+  </si>
+  <si>
+    <t>Negative</t>
   </si>
   <si>
     <t>Low</t>
@@ -477,80 +381,6 @@
     <t>Titles grounded live 2026-08-27 from the pre-rendered DOM. ⚠️ All five share the SINGLE qid "cHeader-hlp-6" — when automated they must be addressed by text or index, never by qid. Same trap class as "t-prd-cmp-cntr-1" (admin-shared.md §B3), and the same shape as the cFooter-9 duplication the footer selectors already work around with an aria-label qualifier. What each topic OPENS was not captured — [ASSUMED] and out of scope for this case.</t>
   </si>
   <si>
-    <t>TST_ASHL_TC_5</t>
-  </si>
-  <si>
-    <t>Verify all five school tabs are shown with Classes active when a school is opened</t>
-  </si>
-  <si>
-    <t>#11 — Verify different tab navigation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click a school card on "My school accounts".
-2. Observe the tab strip and which tab is active.
-3. Observe the page heading and the browser tab title.</t>
-  </si>
-  <si>
-    <t>School: "3 July Test School 1" (&lt;SCHOOL_KEY&gt;)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exactly FIVE tabs are shown, in this order and in upper case:
-CLASSES · STUDENTS · STAFF · LIBRARY · REPORTS
-"CLASSES" is the active tab by default, the page heading shows the school name, and the browser tab reads "Classes | Cambridge One".</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. Tab qids "aDetail-1" (Classes), "aDetail-2" (Students), "aDetail-4" (Staff), "aDetail-5" (Library), "aDetail-6" (Reports). ⚠️ "aDetail-3" IS SKIPPED — the sequence is 1,2,4,5,6. Do not iterate 1..5 assuming contiguity. ⚠️ THE ACTIVE MARKER IS ON THE PARENT &lt;li&gt;, not the anchor: "li.nav-item.active &gt; a". The anchor className is identical on every tab whether active or not, so asserting on the link class is a guaranteed false green. Labels render UPPER CASE — confirm whether that is CSS text-transform or the actual text before asserting case-sensitively.</t>
-  </si>
-  <si>
-    <t>TST_ASHL_TC_6</t>
-  </si>
-  <si>
-    <t>Verify each tab loads its own page and becomes the active tab when it is selected</t>
-  </si>
-  <si>
-    <t>Logged in as school-admin &lt;ADMIN_USER&gt; on Thor; "My school accounts" (/admin/admin/dashboard) displayed. A school is open on the Classes tab.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click "STUDENTS" and note the URL, title and active tab.
-2. Repeat for "STAFF", "LIBRARY", "REPORTS", then "CLASSES".</t>
-  </si>
-  <si>
-    <t>School slug: org_&lt;SCHOOL_SLUG&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each tab navigates to its own URL, sets its own browser-tab title, and becomes the active tab:
-| Tab | URL suffix | Title |
-| CLASSES | /class | "Classes \| Cambridge One" |
-| STUDENTS | /learner | "Students \| Cambridge One" |
-| STAFF | /staff | "Staff \| Cambridge One" |
-| LIBRARY | /library | "Library \| Cambridge One" |
-| REPORTS | /reports | "Reports \| Cambridge One" |
-The school heading stays unchanged throughout.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27 — all five walked and every URL and title confirmed. ⚠️ NOTE the STUDENTS tab routes to "/learner", NOT "/student". A URL assertion built from the tab label will fail on this one. Tabs carry REAL hrefs (unlike the footer, whose logged-in hrefs collapse to javascript:void(0) — TST_FOOT_TC_10 remarks), so tab navigation is genuinely href-driven. TIMING measured this session: Reports took ~4.3 s to become active, Classes ~1.2 s. Poll for "li.nav-item.active &gt; a" carrying the expected qid rather than using a fixed pause (admin-shared.md §B8).</t>
-  </si>
-  <si>
-    <t>TST_ASHL_TC_7</t>
-  </si>
-  <si>
-    <t>Verify the active school tab is identifiable to assistive technology</t>
-  </si>
-  <si>
-    <t>Logged in as school-admin &lt;ADMIN_USER&gt; on Thor; "My school accounts" (/admin/admin/dashboard) displayed. A school is open.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Inspect each tab link for an aria-current or selected-state attribute.
-2. Switch tabs and re-inspect.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The active tab exposes an accessible current/selected state, so assistive technology can announce which section the user is in.
-ACTUAL (2026-08-27): this FAILS. No tab link carries aria-current or aria-selected; the only indicator is the "active" CSS class on the parent &lt;li&gt;, which is presentational.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. This is the SECOND instance of the same gap in this batch — the My Profile tabs have it too (TST_MYPR_TC_8). Worth raising as one combined accessibility ticket rather than two. The school tabs are at least recoverable for automation via "li.nav-item.active"; the profile tabs have no indicator at all, which makes them the more severe of the two.</t>
-  </si>
-  <si>
     <t>TST_FOOT_TC_10</t>
   </si>
   <si>
@@ -711,34 +541,13 @@
     <t>BLOCKED at design time 2026-08-27 on TWO counts: (1) no non-MQA admin account is available — &lt;ADMIN_USER&gt;'s home school IS MQA Sierra School (MQA-ABC-DEF); (2) the product team must first define what technically marks a product as MQA/CQA-restricted. Unblock with a non-MQA admin account and that definition.</t>
   </si>
   <si>
-    <t>TST_SADB_TC_2</t>
-  </si>
-  <si>
-    <t>Verify every school the administrator manages is listed when My school accounts is opened</t>
+    <t>TST_SADB_TC_3</t>
+  </si>
+  <si>
+    <t>Verify switching between organisations loads each one independently when the admin manages several</t>
   </si>
   <si>
     <t>#10 — Admin part of multiple org</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Observe the "My school accounts" page.
-2. Inspect each school card.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every school the administrator manages is listed, one card each, numbered sequentially from "01" with zero padding.
-Each card shows: index, school name, address, the label "School key", the key itself in XXX-XXX-XXX format, a "Copy" control, and a chevron opening the school.
-Observed 2026-08-27 for &lt;ADMIN_USER&gt;: 7 schools, numbered 01–07.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. Card qid "aDashboard-N" (a.inst-link); chevron is a SEPARATE "aDashboard1-N". Both are POSITIONAL. The school key is carried in the card's aria-label, which is what makes key-based selection possible (schoolAdminDashboard.schoolLinkByKey uses a.inst-link[aria-label*="{{key}}"]).
-⚠️ NEVER assert the literal count 7 — this is a shared account and the list changes (admin-shared.md §A5). Assert the card STRUCTURE and that the expected key is present.
-Extends the existing SADB module (TST_SADB_TC_1 opens a school by key) — that case already covers opening; this one covers the LISTING, which nothing did.
-⚠️ EXTENDS admin-shared.md §0, which documents 4 schools. This account sees 7 — KNF-XRD-QVE, HQC-ZWM-ZVF and GYB-JMU-KYA were undocumented.</t>
-  </si>
-  <si>
-    <t>TST_SADB_TC_3</t>
-  </si>
-  <si>
-    <t>Verify switching between organisations loads each one independently when the admin manages several</t>
   </si>
   <si>
     <t xml:space="preserve">1. Open the first school and note the org slug in the URL and the page heading.
@@ -757,31 +566,6 @@
 ⚠️ The org slug is NOT derivable from the school name or key — "3 July Test School 1" (FCN-CHZ-PDA) maps to org_perf_testschool_1. Capture each slug; never construct it.
 The school context MUST be set by clicking the card — deep-linking /admin/admin/org_&lt;slug&gt;/class returns /dashboard/error even when authenticated (admin-shared.md §A1).
 Worth checking whether the per-account server-side class Filter and Search (§A4) are scoped per school or leak across organisations — that is unknown and would be a real defect if they leak.</t>
-  </si>
-  <si>
-    <t>TST_SADB_TC_4</t>
-  </si>
-  <si>
-    <t>Verify two schools sharing a display name remain distinguishable by their school key</t>
-  </si>
-  <si>
-    <t>#12 — Verify viewing multiple schools</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Locate the two cards sharing the same display name.
-2. Compare their school keys.
-3. Open the one matching a specific key and confirm which school loaded.</t>
-  </si>
-  <si>
-    <t>Duplicate display name "3 July Test School 1" — keys FCN-CHZ-PDA and ZPB-TWP-AEQ</t>
-  </si>
-  <si>
-    <t>Both cards show the SAME display name but DIFFERENT school keys, and the card selected by key opens that specific school.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27 — cards 01 and 02 both read "3 July Test School 1" with keys FCN-CHZ-PDA and ZPB-TWP-AEQ, and identical addresses too.
-⚠️ THIS IS THE CASE THAT JUSTIFIES admin-shared.md §0's standing rule: ALWAYS select a school by KEY, never by name or card position. Selecting by name is ambiguous here, and card qids (aDashboard-N) are positional so they re-issue when the list changes.
-Confirming WHICH school loaded (step 3) needs a distinguishing feature — the org slug in the URL is the reliable one, since the heading shows the shared name.</t>
   </si>
   <si>
     <t>TST_SRQS_TC_2</t>
@@ -839,66 +623,6 @@
     <t>**[CORRECTED 2026-09-14 — live pass]** VERIFIED LIVE 2026-09-14 — walked to the summary, never submitted. Next is NATIVELY disabled (disabled attribute + .disabled + pointer-events none), so an isEnabled assertion is valid. The wizard advances IN-PAGE (URL never changes) and the Next qid differs per step. ⚠️ The existing wizard modules' generic "button.btn-purple" also matches "Send Request" (t-ss-as-btn-1) — stop by qid. The summary omits school type and number of teachers. — Superseded note follows: ⚠️ EXPECTED RESULT NOT VERIFIED — the wizard was not walked in this session. INFERRED from the existing automation, whose case titles state the enabling direction only, e.g. TST_SCTY_TC_3 "Select first radio option (Primary school) to ENABLE Next button" and TST_SNAM_TC_3 "Fill school name field to ENABLE Next button". The DISABLED half is nowhere asserted, which is the gap this case fills. Confirm whether Next is natively disabled or only CSS-disabled — admin-shared.md §B4 records CSS-only disabling elsewhere in this app, which would make a naive enabled-state check a false green. SIDE-EFFECT FREE: stops short of submission.</t>
   </si>
   <si>
-    <t>TST_ASHL_TC_8</t>
-  </si>
-  <si>
-    <t>Verify no dialog is visible when an admin screen first loads</t>
-  </si>
-  <si>
-    <t>#9 — Verify various errors in forms and modals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Load the Classes tab and observe the screen without interacting.
-2. Repeat for Students, Staff, Library and Reports.</t>
-  </si>
-  <si>
-    <t>On every tab, no dialog, warning or error is visible on load. The screen shows only its own content.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27 — verified that every dialog present in the DOM was hidden on load (Classes 5, Students 4, Staff 1; all offsetParent === null). ⚠️ THIS IS THE HEADLINE AUTOMATION TRAP FOR THIS SCENARIO. Admin dialogs are PRE-RENDERED, so they exist in the DOM before anything triggers them. Any check of the form "getElementCount(dialog) &gt; 0" therefore passes ALWAYS and proves nothing — admin-shared.md §B2 records this silently breaking reset_filters for weeks. Assert VISIBILITY, never presence. Note also that opacity:0 still counts as visible to Playwright; only display:none is hidden.</t>
-  </si>
-  <si>
-    <t>TST_ASHL_TC_9</t>
-  </si>
-  <si>
-    <t>Verify the 50-item limit warnings use a consistent message pattern across screens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Read the bulk-limit warning offered on the Classes tab.
-2. Read the equivalent warning on the Students tab.
-3. Compare their wording.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Both follow the same two-line pattern, differing only in the noun:
-Classes: "You can only delete 50 classes at one time" / "Please uncheck some classes to continue"
-Students: "You can only remove 50 students at one time" / "Please uncheck some students to continue"
-Both offer a "Close" control.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. COPY GROUNDED LIVE 2026-08-27 — both captured VERBATIM from the pre-rendered DOM (§A6) without reaching the capped state, which would otherwise require 51+ rows. Note the VERB differs with the domain — "delete" for classes, "remove" for students — so a single shared assertion string is wrong. The LIMIT (50) and the sentence shape are the consistent parts. Reaching these states for real is Blocked on the shared school (admin-shared.md §A5: it holds 26 students, so the 50-student cap cannot be hit).</t>
-  </si>
-  <si>
-    <t>TST_ASHL_TC_10</t>
-  </si>
-  <si>
-    <t>Verify destructive confirmations state their consequence before the action is taken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Read the class-deletion confirmation.
-2. Read the student-removal confirmation.
-3. Read the change-school-key confirmation.
-4. Check each offers a way to back out.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each destructive confirmation names its consequence and offers a non-destructive exit:
-Class delete — "WARNING!" / "There might be students, teachers and course materials in the selected classes" / "Are you sure you want to delete?" / "No, cancel"
-Student removal — "I confirm that I want to remove students from my school account" / "Cancel" / "Request to remove"
-Change school key — "CAREFUL!" / "Changing the school key cannot be undone" / "Cancel"</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. ALL THREE CAPTURED VERBATIM 2026-08-27 from the pre-rendered DOM, without triggering any of them — which is the only safe way, since all three are destructive on a shared school. ⚠️ The change-school-key dialog is present on EVERY admin tab (Classes, Students, Staff all carry it) because School settings lives in the shared page chrome — scope any modal selector with :has(...) to the specific dialog, or it will match this one everywhere. Async follow-ups are also pre-rendered and worth checking in the same pass: "This will take a few minutes" (classes) and "Removing students may take some time" (students).</t>
-  </si>
-  <si>
     <t>TST_SADB_TC_5</t>
   </si>
   <si>
@@ -920,28 +644,6 @@
   </si>
   <si>
     <t>**[CORRECTED 2026-09-14 — live pass]** Toggling back returns to the admin page the round trip STARTED on (verified from /class on 2026-09-14), so start this case on the dashboard. Do NOT assert the document title — it varies with the load path ("Administrator | Cambridge One" vs "My school accounts | Cambridge One"). — Superseded note follows: GROUNDED LIVE 2026-08-27 — the full round trip was performed and the account was left in Administrator view. ⚠️ THE SWITCH ELEMENT IS NAMED DIFFERENTLY IN EACH VIEW: ".can-toggle__switch" (double underscore) in the admin view, ".can-toggle-switch" (single hyphen) in the teacher view. A selector written for one view SILENTLY FAILS to find it in the other, which breaks exactly the round trip this case exercises. Use "#teacher-admin-toggle" (stable in both) and read the input's checked state — false = Administrator, true = Teacher. The focusable control is the inner [tabindex="0"] div; the input itself is aria-hidden. The toggle also appears on inner admin tabs, not just the dashboard. Existing selector schoolAdminDashboard.teacherAdminToggle already targets the input; this extends SADB. SIDE-EFFECT FREE — a view switch only.</t>
-  </si>
-  <si>
-    <t>TST_SADB_TC_6</t>
-  </si>
-  <si>
-    <t>Verify the teacher view lists the schools where the user teaches, not those they administer</t>
-  </si>
-  <si>
-    <t>Logged in as school-admin &lt;ADMIN_USER&gt; on Thor; "My school accounts" (/admin/admin/dashboard) displayed. The user is both an administrator and a teacher on overlapping sets of schools.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. On "My school accounts", list the schools shown.
-2. Switch to the teacher view.
-3. List the school groups shown there.
-4. Compare the two lists.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The two lists are NOT the same. The administrator view shows schools the user administers; the teacher view groups classes under schools where the user teaches, which may include schools absent from the administrator view.
-Observed 2026-08-27: administrator view 7 schools; teacher view 8 school groups, including "ABERYSTWYTH COLLEGE : THOR" and "LTI INTEGRATIONS TEST2", neither of which appears in the administrator list.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. GROUNDED LIVE 2026-08-27. This matters because it is easy to assume the two views show the same estate — they do not, and a test asserting equal school counts across the toggle will fail. ⚠️ The teacher view groups by school DISPLAY NAME, so the two distinct schools both called "3 July Test School 1" (FCN-CHZ-PDA and ZPB-TWP-AEQ) collapse into a SINGLE group there. The admin view keeps them separate via their keys. Do not match schools across the two views by name. ⚠️ NEVER assert the literal counts 7 and 8 — shared account (§A5). Assert the RELATIONSHIP: the teacher list contains at least one school the admin list does not. ⚠️ Every "Create class" button in the teacher view shares qid "tDashboard-ncls-btn-1" — 7 elements, one per school group. See TST_SADB_TC_7.</t>
   </si>
   <si>
     <t>TST_SADB_TC_7</t>
@@ -977,6 +679,9 @@
 The teacher view groups by display name, so a school with a duplicate name is ambiguous here — pick a school with a UNIQUE name (§A5, TST_SADB_TC_6).</t>
   </si>
   <si>
+    <t>Not Run</t>
+  </si>
+  <si>
     <t>Not Automated</t>
   </si>
   <si>
@@ -1064,6 +769,9 @@
   </si>
   <si>
     <t>Verify data stays scoped to the active organisation when an admin manages several schools</t>
+  </si>
+  <si>
+    <t>#11 — Verify different tab navigation</t>
   </si>
   <si>
     <t>An administrator with access to two or more schools, where each school holds at least one record (class, student, staff member, library product) that exists **only** in that school.</t>
@@ -1473,7 +1181,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P42"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1843,7 +1551,7 @@
     </row>
     <row r="8" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>61</v>
@@ -1852,157 +1560,157 @@
         <v>62</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="L8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>75</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>74</v>
@@ -2011,69 +1719,69 @@
         <v>56</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>26</v>
@@ -2093,16 +1801,16 @@
     </row>
     <row r="13" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>19</v>
@@ -2114,16 +1822,16 @@
         <v>21</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>26</v>
@@ -2143,37 +1851,37 @@
     </row>
     <row r="14" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>56</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>26</v>
@@ -2193,37 +1901,37 @@
     </row>
     <row r="15" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>56</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>26</v>
@@ -2243,37 +1951,37 @@
     </row>
     <row r="16" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>26</v>
@@ -2293,16 +2001,16 @@
     </row>
     <row r="17" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>19</v>
@@ -2311,19 +2019,19 @@
         <v>20</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>26</v>
@@ -2343,57 +2051,57 @@
     </row>
     <row r="18" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>21</v>
+        <v>124</v>
       </c>
       <c r="H18" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M18" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="I18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J18" s="2" t="s">
+      <c r="N18" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="O18" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="P18" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>132</v>
@@ -2402,16 +2110,16 @@
         <v>133</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>20</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>135</v>
@@ -2429,21 +2137,21 @@
         <v>26</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>139</v>
@@ -2452,178 +2160,178 @@
         <v>140</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>20</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>26</v>
+        <v>147</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>70</v>
+        <v>129</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>71</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
+        <v>28</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="G21" s="2" t="s">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>23</v>
+        <v>152</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>21</v>
+        <v>158</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>26</v>
+        <v>163</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>29</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>26</v>
@@ -2643,16 +2351,16 @@
     </row>
     <row r="24" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>19</v>
@@ -2661,19 +2369,19 @@
         <v>20</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>26</v>
@@ -2693,16 +2401,16 @@
     </row>
     <row r="25" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>19</v>
@@ -2711,884 +2419,234 @@
         <v>20</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>178</v>
+        <v>26</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="I26" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M26" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="J26" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="N26" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>28</v>
+        <v>194</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>29</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>189</v>
+        <v>141</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>177</v>
+        <v>129</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>177</v>
+        <v>129</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>179</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>198</v>
+        <v>106</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>21</v>
+        <v>206</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>23</v>
+        <v>208</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>21</v>
+        <v>214</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="N30" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="P30" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
-        <v>30</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="N31" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="O31" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="P31" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
-        <v>31</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N32" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P32" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
-        <v>32</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="N33" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O33" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="P33" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
-        <v>33</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="N34" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O34" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="P34" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
-        <v>34</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="N35" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="P35" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
-        <v>35</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N36" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P36" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
-        <v>36</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M37" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="N37" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O37" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="P37" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
-        <v>37</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
-        <v>38</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="N39" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O39" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="P39" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
-        <v>39</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="O40" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="P40" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
-        <v>40</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M41" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O41" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P41" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="P42" s="2" t="s">
-        <v>179</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
